--- a/All Salons 08.14.26.xlsx
+++ b/All Salons 08.14.26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffd\OneDrive\Desktop\GC-Weekly-Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E63A9D49-1223-40DF-B1DF-FCE5433C79B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A48235-6484-4108-B13B-6C50F4CBF156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,12 +357,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00%;\-#,##0.00%;#,##0.00%"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0%;\-#,##0.0%;#,##0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.0%;\-0.0%;0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00;\(\$#,##0.00\);\$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00%;\-#,##0.00%;#,##0.00%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0%;\-#,##0.0%;#,##0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0%;\-0.0%;0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0.00;\(\$#,##0.00\);\$#,##0.00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -433,10 +433,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -445,25 +448,25 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -472,31 +475,20 @@
     <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -522,7 +514,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:S92">
   <autoFilter ref="A1:S92" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S92">
-    <sortCondition sortBy="cellColor" ref="C1:C92" dxfId="1"/>
+    <sortCondition ref="C1:C92"/>
   </sortState>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Salon"/>
@@ -902,235 +894,239 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="12">
-        <v>46248</v>
-      </c>
-      <c r="C2" s="13">
-        <v>292</v>
-      </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="13">
-        <v>90</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.30821917808219179</v>
-      </c>
-      <c r="H2" s="16">
-        <v>0.46700000000000003</v>
-      </c>
-      <c r="I2" s="15">
-        <v>0.69</v>
-      </c>
-      <c r="J2" s="13">
-        <v>150.52000000000001</v>
-      </c>
-      <c r="K2" s="15">
-        <v>0.29799999999999999</v>
-      </c>
-      <c r="L2" s="11">
-        <v>150.52000000000001</v>
-      </c>
-      <c r="M2" s="15">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="N2" s="15">
-        <v>0.28199999999999997</v>
-      </c>
-      <c r="O2" s="17">
-        <v>7.4297945205479454</v>
-      </c>
-      <c r="P2" s="18">
-        <v>16.323826714801449</v>
-      </c>
-      <c r="Q2" s="18">
-        <v>1.9513646295773801</v>
-      </c>
-      <c r="R2" s="19">
-        <v>38.333776242359818</v>
-      </c>
-      <c r="S2" s="15">
-        <v>0.10530329289428079</v>
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C2" s="4">
+        <v>243</v>
+      </c>
+      <c r="D2" s="4">
+        <v>305</v>
+      </c>
+      <c r="E2" s="5">
+        <v>-0.20327868852459019</v>
+      </c>
+      <c r="F2" s="4">
+        <v>52</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.2139917695473251</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.747</v>
+      </c>
+      <c r="J2" s="4">
+        <v>145.72</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0.315</v>
+      </c>
+      <c r="L2" s="2">
+        <v>-19.650000000000009</v>
+      </c>
+      <c r="M2" s="6">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0.156</v>
+      </c>
+      <c r="O2" s="8">
+        <v>6.632921810699588</v>
+      </c>
+      <c r="P2" s="9">
+        <v>16.561802575107301</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>1.697013499790986</v>
+      </c>
+      <c r="R2" s="10">
+        <v>34.332967334614331</v>
+      </c>
+      <c r="S2" s="6">
+        <v>0.15003397961223269</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B3" s="12">
         <v>46248</v>
       </c>
       <c r="C3" s="13">
-        <v>424</v>
+        <v>248</v>
       </c>
       <c r="D3" s="13">
-        <v>421</v>
+        <v>247</v>
       </c>
       <c r="E3" s="14">
-        <v>7.1258907363420431E-3</v>
+        <v>4.048582995951417E-3</v>
       </c>
       <c r="F3" s="13">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G3" s="15">
-        <v>0.19103773584905659</v>
+        <v>0.25806451612903231</v>
       </c>
       <c r="H3" s="16">
-        <v>0.36399999999999999</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="I3" s="15">
-        <v>0.746</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="J3" s="13">
-        <v>209.43</v>
+        <v>130.88</v>
       </c>
       <c r="K3" s="15">
-        <v>0.25</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="L3" s="11">
-        <v>22.56</v>
+        <v>-0.36000000000001359</v>
       </c>
       <c r="M3" s="15">
-        <v>0.25700000000000001</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="N3" s="15">
-        <v>0.41499999999999998</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="O3" s="17">
-        <v>9.6146226415094329</v>
+        <v>5.8221774193548388</v>
       </c>
       <c r="P3" s="18">
-        <v>17.747394540942931</v>
+        <v>14.07025862068966</v>
       </c>
       <c r="Q3" s="18">
-        <v>2.0549539055425869</v>
+        <v>1.954996125455708</v>
       </c>
       <c r="R3" s="19">
-        <v>40.118416654729501</v>
+        <v>39.746332518337411</v>
       </c>
       <c r="S3" s="15">
-        <v>0.1239887841546355</v>
+        <v>0.1148046111762407</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="12">
-        <v>46248</v>
-      </c>
-      <c r="C4" s="13">
-        <v>518</v>
-      </c>
-      <c r="D4" s="13">
-        <v>396</v>
-      </c>
-      <c r="E4" s="14">
-        <v>0.30808080808080812</v>
-      </c>
-      <c r="F4" s="13">
-        <v>105</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0.20270270270270269</v>
-      </c>
-      <c r="H4" s="16">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="I4" s="15">
-        <v>0.71099999999999997</v>
-      </c>
-      <c r="J4" s="13">
-        <v>184.78</v>
-      </c>
-      <c r="K4" s="15">
-        <v>0.33700000000000002</v>
-      </c>
-      <c r="L4" s="11">
-        <v>25.37</v>
-      </c>
-      <c r="M4" s="15">
-        <v>0.125</v>
-      </c>
-      <c r="N4" s="15">
-        <v>0.122</v>
-      </c>
-      <c r="O4" s="17">
-        <v>4.807722007722008</v>
-      </c>
-      <c r="P4" s="18">
-        <v>15.22464646464646</v>
-      </c>
-      <c r="Q4" s="18">
-        <v>2.853295191570838</v>
-      </c>
-      <c r="R4" s="19">
-        <v>55.850200238121012</v>
-      </c>
-      <c r="S4" s="15">
-        <v>0.1107237354085603</v>
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C4" s="4">
+        <v>286</v>
+      </c>
+      <c r="D4" s="4">
+        <v>313</v>
+      </c>
+      <c r="E4" s="5">
+        <v>-8.6261980830670923E-2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>84</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.2937062937062937</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="J4" s="4">
+        <v>155.75</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="L4" s="2">
+        <v>-7.6399999999999864</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="O4" s="8">
+        <v>6.668881118881119</v>
+      </c>
+      <c r="P4" s="9">
+        <v>17.631297709923661</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1.84400417772089</v>
+      </c>
+      <c r="R4" s="10">
+        <v>37.06581059390048</v>
+      </c>
+      <c r="S4" s="6">
+        <v>9.8813884528170248E-2</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="12">
-        <v>46248</v>
-      </c>
-      <c r="C5" s="13">
-        <v>248</v>
-      </c>
-      <c r="D5" s="13">
-        <v>247</v>
-      </c>
-      <c r="E5" s="14">
-        <v>4.048582995951417E-3</v>
-      </c>
-      <c r="F5" s="13">
-        <v>64</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0.25806451612903231</v>
-      </c>
-      <c r="H5" s="16">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="I5" s="15">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="J5" s="13">
-        <v>130.88</v>
-      </c>
-      <c r="K5" s="15">
-        <v>0.26200000000000001</v>
-      </c>
-      <c r="L5" s="11">
-        <v>-0.36000000000001359</v>
-      </c>
-      <c r="M5" s="15">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="N5" s="15">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="O5" s="17">
-        <v>5.8221774193548388</v>
-      </c>
-      <c r="P5" s="18">
-        <v>14.07025862068966</v>
-      </c>
-      <c r="Q5" s="18">
-        <v>1.954996125455708</v>
-      </c>
-      <c r="R5" s="19">
-        <v>39.746332518337411</v>
-      </c>
-      <c r="S5" s="15">
-        <v>0.1148046111762407</v>
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C5" s="4">
+        <v>287</v>
+      </c>
+      <c r="D5" s="4">
+        <v>402</v>
+      </c>
+      <c r="E5" s="5">
+        <v>-0.28606965174129351</v>
+      </c>
+      <c r="F5" s="4">
+        <v>71</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.2473867595818815</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="J5" s="4">
+        <v>151.35</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="L5" s="2">
+        <v>-47.31</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="O5" s="8">
+        <v>12.58432055749129</v>
+      </c>
+      <c r="P5" s="9">
+        <v>16.6945652173913</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>1.9318385453428371</v>
+      </c>
+      <c r="R5" s="10">
+        <v>36.868186323092168</v>
+      </c>
+      <c r="S5" s="6">
+        <v>0.15555012667390519</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -1190,3660 +1186,3656 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3">
         <v>46248</v>
       </c>
       <c r="C7" s="4">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="D7" s="4">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="E7" s="5">
-        <v>0.16379310344827591</v>
+        <v>1.748251748251748E-2</v>
       </c>
       <c r="F7" s="4">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="G7" s="6">
-        <v>0.25432098765432098</v>
+        <v>0.23024054982817871</v>
       </c>
       <c r="H7" s="7">
-        <v>0.36099999999999999</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="I7" s="6">
-        <v>0.69299999999999995</v>
+        <v>0.71799999999999997</v>
       </c>
       <c r="J7" s="4">
-        <v>164.09</v>
+        <v>140.15</v>
       </c>
       <c r="K7" s="6">
-        <v>0.254</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="L7" s="2">
-        <v>9.7199999999999989</v>
+        <v>-9.3199999999999932</v>
       </c>
       <c r="M7" s="6">
-        <v>0.104</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="N7" s="6">
-        <v>8.3000000000000004E-2</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="O7" s="8">
-        <v>4.8708641975308646</v>
+        <v>8.5120274914089347</v>
       </c>
       <c r="P7" s="9">
-        <v>14.19922279792746</v>
+        <v>15.806115107913669</v>
       </c>
       <c r="Q7" s="9">
-        <v>2.5042798962565782</v>
+        <v>2.125144580278056</v>
       </c>
       <c r="R7" s="10">
-        <v>51.965384849777557</v>
+        <v>43.503389225829473</v>
       </c>
       <c r="S7" s="6">
-        <v>9.461728395061729E-2</v>
+        <v>0.32671313760866</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46248</v>
-      </c>
-      <c r="C8" s="4">
-        <v>520</v>
-      </c>
-      <c r="D8" s="4">
-        <v>475</v>
-      </c>
-      <c r="E8" s="5">
-        <v>9.4736842105263161E-2</v>
-      </c>
-      <c r="F8" s="4">
-        <v>103</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.19807692307692309</v>
-      </c>
-      <c r="H8" s="7">
-        <v>0.35299999999999998</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.77400000000000002</v>
-      </c>
-      <c r="J8" s="4">
-        <v>199.61</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="L8" s="2">
-        <v>17.710000000000012</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0.107</v>
-      </c>
-      <c r="O8" s="8">
-        <v>6.2301923076923069</v>
-      </c>
-      <c r="P8" s="9">
-        <v>15.781000000000001</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>2.627345009980556</v>
-      </c>
-      <c r="R8" s="10">
-        <v>53.078503081007959</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0.16363190184049081</v>
+      <c r="A8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46248</v>
+      </c>
+      <c r="C8" s="13">
+        <v>292</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="13">
+        <v>90</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.30821917808219179</v>
+      </c>
+      <c r="H8" s="16">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.69</v>
+      </c>
+      <c r="J8" s="13">
+        <v>150.52000000000001</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="L8" s="11">
+        <v>150.52000000000001</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="O8" s="17">
+        <v>7.4297945205479454</v>
+      </c>
+      <c r="P8" s="18">
+        <v>16.323826714801449</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>1.9513646295773801</v>
+      </c>
+      <c r="R8" s="19">
+        <v>38.333776242359818</v>
+      </c>
+      <c r="S8" s="15">
+        <v>0.10530329289428079</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3">
         <v>46248</v>
       </c>
       <c r="C9" s="4">
-        <v>390</v>
+        <v>303</v>
       </c>
       <c r="D9" s="4">
-        <v>426</v>
+        <v>270</v>
       </c>
       <c r="E9" s="5">
-        <v>-8.4507042253521125E-2</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="F9" s="4">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="G9" s="6">
-        <v>0.241025641025641</v>
+        <v>0.40924092409240931</v>
       </c>
       <c r="H9" s="7">
-        <v>0.34300000000000003</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="I9" s="6">
-        <v>0.69599999999999995</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="J9" s="4">
-        <v>167.9</v>
+        <v>159.24</v>
       </c>
       <c r="K9" s="6">
-        <v>0.33400000000000002</v>
+        <v>0.31</v>
       </c>
       <c r="L9" s="2">
-        <v>-38.53</v>
+        <v>10.09</v>
       </c>
       <c r="M9" s="6">
-        <v>0.28199999999999997</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="N9" s="6">
-        <v>0.33300000000000002</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="O9" s="8">
-        <v>10.676410256410261</v>
+        <v>12.28415841584158</v>
       </c>
       <c r="P9" s="9">
-        <v>16.845161290322579</v>
+        <v>16.982899628252792</v>
       </c>
       <c r="Q9" s="9">
-        <v>2.356835715437275</v>
+        <v>1.9815039763571829</v>
       </c>
       <c r="R9" s="10">
-        <v>50.160810005955923</v>
+        <v>40.448379804069333</v>
       </c>
       <c r="S9" s="6">
-        <v>0.19933333333333331</v>
+        <v>0.15649743828598051</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3">
         <v>46248</v>
       </c>
       <c r="C10" s="4">
-        <v>471</v>
+        <v>318</v>
       </c>
       <c r="D10" s="4">
-        <v>494</v>
+        <v>260</v>
       </c>
       <c r="E10" s="5">
-        <v>-4.6558704453441298E-2</v>
+        <v>0.22307692307692309</v>
       </c>
       <c r="F10" s="4">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="G10" s="6">
-        <v>0.20806794055201699</v>
+        <v>0.25786163522012578</v>
       </c>
       <c r="H10" s="7">
-        <v>0.34300000000000003</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="I10" s="6">
-        <v>0.76800000000000002</v>
+        <v>0.755</v>
       </c>
       <c r="J10" s="4">
-        <v>197.03</v>
+        <v>175.38</v>
       </c>
       <c r="K10" s="6">
-        <v>0.29499999999999998</v>
+        <v>0.315</v>
       </c>
       <c r="L10" s="2">
-        <v>-22.150000000000009</v>
+        <v>19.039999999999988</v>
       </c>
       <c r="M10" s="6">
-        <v>0.108</v>
+        <v>0.129</v>
       </c>
       <c r="N10" s="6">
-        <v>0.14000000000000001</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="O10" s="8">
-        <v>5.1968152866242026</v>
+        <v>5.2062893081761006</v>
       </c>
       <c r="P10" s="9">
-        <v>14.0718820861678</v>
+        <v>16.116107382550339</v>
       </c>
       <c r="Q10" s="9">
-        <v>2.415816460600329</v>
+        <v>1.850250752796174</v>
       </c>
       <c r="R10" s="10">
-        <v>46.348271836776128</v>
+        <v>39.23480442467784</v>
       </c>
       <c r="S10" s="6">
-        <v>7.5732351000659781E-2</v>
+        <v>0.11128033716029651</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3">
         <v>46248</v>
       </c>
       <c r="C11" s="4">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D11" s="4">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="E11" s="5">
-        <v>-0.1066666666666667</v>
+        <v>2.180685358255452E-2</v>
       </c>
       <c r="F11" s="4">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="G11" s="6">
-        <v>0.1253731343283582</v>
+        <v>0.29878048780487798</v>
       </c>
       <c r="H11" s="7">
-        <v>0.33300000000000002</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="I11" s="6">
-        <v>0.78800000000000003</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="J11" s="4">
-        <v>168.24</v>
+        <v>159.82</v>
       </c>
       <c r="K11" s="6">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="L11" s="2">
-        <v>13.41</v>
+        <v>-2.7800000000000011</v>
       </c>
       <c r="M11" s="6">
-        <v>0.113</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="N11" s="6">
-        <v>0.08</v>
+        <v>0.104</v>
       </c>
       <c r="O11" s="8">
-        <v>4.7205970149253744</v>
+        <v>4.3213414634146341</v>
       </c>
       <c r="P11" s="9">
-        <v>15.931076923076921</v>
+        <v>12.36440129449838</v>
       </c>
       <c r="Q11" s="9">
-        <v>2.0082684150721581</v>
+        <v>2.089501274179101</v>
       </c>
       <c r="R11" s="10">
-        <v>42.415596766524011</v>
+        <v>42.003503941934682</v>
       </c>
       <c r="S11" s="6">
-        <v>0.13507146860986549</v>
+        <v>0.15270642889255209</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3">
         <v>46248</v>
       </c>
       <c r="C12" s="4">
-        <v>560</v>
+        <v>331</v>
       </c>
       <c r="D12" s="4">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="E12" s="5">
-        <v>0.2147505422993492</v>
+        <v>-4.6109510086455328E-2</v>
       </c>
       <c r="F12" s="4">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="G12" s="6">
-        <v>0.26964285714285707</v>
+        <v>0.29607250755287012</v>
       </c>
       <c r="H12" s="7">
-        <v>0.32300000000000001</v>
+        <v>0.221</v>
       </c>
       <c r="I12" s="6">
-        <v>0.76800000000000002</v>
+        <v>0.72899999999999998</v>
       </c>
       <c r="J12" s="4">
-        <v>199.2</v>
+        <v>163.82</v>
       </c>
       <c r="K12" s="6">
-        <v>0.317</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="L12" s="2">
-        <v>9.8699999999999761</v>
+        <v>-19.36000000000001</v>
       </c>
       <c r="M12" s="6">
-        <v>0.24099999999999999</v>
+        <v>0.245</v>
       </c>
       <c r="N12" s="6">
-        <v>0.309</v>
+        <v>0.24</v>
       </c>
       <c r="O12" s="8">
-        <v>10.73964285714286</v>
+        <v>10.02870090634441</v>
       </c>
       <c r="P12" s="9">
-        <v>14.61047794117647</v>
+        <v>16.05103448275862</v>
       </c>
       <c r="Q12" s="9">
-        <v>2.855332654866479</v>
+        <v>2.0888004893419652</v>
       </c>
       <c r="R12" s="10">
-        <v>60.712851405622487</v>
+        <v>41.899645952875112</v>
       </c>
       <c r="S12" s="6">
-        <v>0.1483851496609889</v>
+        <v>6.367340955731457E-2</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3">
         <v>46248</v>
       </c>
       <c r="C13" s="4">
-        <v>488</v>
+        <v>334</v>
       </c>
       <c r="D13" s="4">
-        <v>443</v>
+        <v>378</v>
       </c>
       <c r="E13" s="5">
-        <v>0.1015801354401806</v>
+        <v>-0.1164021164021164</v>
       </c>
       <c r="F13" s="4">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="G13" s="6">
-        <v>0.24180327868852461</v>
+        <v>0.29041916167664672</v>
       </c>
       <c r="H13" s="7">
-        <v>0.32100000000000001</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="I13" s="6">
-        <v>0.747</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="J13" s="4">
-        <v>181.03</v>
+        <v>169.07</v>
       </c>
       <c r="K13" s="6">
-        <v>0.311</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="L13" s="2">
-        <v>4.6599999999999966</v>
+        <v>-3.0600000000000018</v>
       </c>
       <c r="M13" s="6">
-        <v>0.191</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="N13" s="6">
-        <v>0.153</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="O13" s="8">
-        <v>7.8989754098360656</v>
+        <v>7.5565868263473046</v>
       </c>
       <c r="P13" s="9">
-        <v>12.65674518201285</v>
+        <v>16.31047297297297</v>
       </c>
       <c r="Q13" s="9">
-        <v>2.7413645847054671</v>
+        <v>2.0023392187618518</v>
       </c>
       <c r="R13" s="10">
-        <v>57.846765729437109</v>
+        <v>40.533506831489923</v>
       </c>
       <c r="S13" s="6">
-        <v>8.9945569136745604E-2</v>
+        <v>0.10060557420107979</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3">
         <v>46248</v>
       </c>
       <c r="C14" s="4">
-        <v>478</v>
+        <v>335</v>
       </c>
       <c r="D14" s="4">
-        <v>446</v>
+        <v>323</v>
       </c>
       <c r="E14" s="5">
-        <v>7.1748878923766815E-2</v>
+        <v>3.7151702786377708E-2</v>
       </c>
       <c r="F14" s="4">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G14" s="6">
-        <v>0.17573221757322169</v>
+        <v>0.33134328358208948</v>
       </c>
       <c r="H14" s="7">
-        <v>0.31900000000000001</v>
+        <v>0.217</v>
       </c>
       <c r="I14" s="6">
-        <v>0.75600000000000001</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="J14" s="4">
-        <v>202.09</v>
+        <v>176.27</v>
       </c>
       <c r="K14" s="6">
-        <v>0.26400000000000001</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="L14" s="2">
-        <v>-18.849999999999991</v>
+        <v>7.4000000000000057</v>
       </c>
       <c r="M14" s="6">
-        <v>0.115</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="N14" s="6">
-        <v>0.14299999999999999</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="O14" s="8">
-        <v>5.4619246861924688</v>
+        <v>12.161194029850749</v>
       </c>
       <c r="P14" s="9">
-        <v>14.83728070175439</v>
+        <v>19.356393442622949</v>
       </c>
       <c r="Q14" s="9">
-        <v>2.4029885086727472</v>
+        <v>1.906025175791233</v>
       </c>
       <c r="R14" s="10">
-        <v>50.635855311989708</v>
+        <v>38.565836500822599</v>
       </c>
       <c r="S14" s="6">
-        <v>0.1009469363822926</v>
+        <v>0.14636712409620781</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3">
         <v>46248</v>
       </c>
       <c r="C15" s="4">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="D15" s="4">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="E15" s="5">
-        <v>0.13271604938271611</v>
+        <v>-0.1066666666666667</v>
       </c>
       <c r="F15" s="4">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="G15" s="6">
-        <v>0.27520435967302448</v>
+        <v>0.1253731343283582</v>
       </c>
       <c r="H15" s="7">
-        <v>0.317</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="I15" s="6">
-        <v>0.76300000000000001</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="J15" s="4">
-        <v>175.3</v>
+        <v>168.24</v>
       </c>
       <c r="K15" s="6">
-        <v>0.32300000000000001</v>
+        <v>0.312</v>
       </c>
       <c r="L15" s="2">
-        <v>19.79000000000002</v>
+        <v>13.41</v>
       </c>
       <c r="M15" s="6">
-        <v>0.09</v>
+        <v>0.113</v>
       </c>
       <c r="N15" s="6">
-        <v>0.13500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O15" s="8">
-        <v>4.9272479564032698</v>
+        <v>4.7205970149253744</v>
       </c>
       <c r="P15" s="9">
-        <v>14.24327485380117</v>
+        <v>15.931076923076921</v>
       </c>
       <c r="Q15" s="9">
-        <v>2.1878542448045262</v>
+        <v>2.0082684150721581</v>
       </c>
       <c r="R15" s="10">
-        <v>39.794637763833428</v>
+        <v>42.415596766524011</v>
       </c>
       <c r="S15" s="6">
-        <v>9.3709862385321099E-2</v>
+        <v>0.13507146860986549</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B16" s="3">
         <v>46248</v>
       </c>
       <c r="C16" s="4">
-        <v>413</v>
+        <v>346</v>
       </c>
       <c r="D16" s="4">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="E16" s="5">
-        <v>8.9709762532981532E-2</v>
+        <v>4.2168674698795178E-2</v>
       </c>
       <c r="F16" s="4">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G16" s="6">
-        <v>0.1864406779661017</v>
+        <v>0.2774566473988439</v>
       </c>
       <c r="H16" s="7">
-        <v>0.317</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="I16" s="6">
-        <v>0.73299999999999998</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="J16" s="4">
-        <v>187.29</v>
+        <v>155.16</v>
       </c>
       <c r="K16" s="6">
-        <v>0.24099999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="L16" s="2">
-        <v>14.919999999999989</v>
+        <v>1.359999999999985</v>
       </c>
       <c r="M16" s="6">
-        <v>0.107</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="N16" s="6">
-        <v>8.7999999999999995E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="O16" s="8">
-        <v>4.8142857142857141</v>
+        <v>2.9710982658959542</v>
       </c>
       <c r="P16" s="9">
-        <v>15.094736842105259</v>
+        <v>12.665060240963861</v>
       </c>
       <c r="Q16" s="9">
-        <v>2.2413260746773229</v>
+        <v>2.2704164949244312</v>
       </c>
       <c r="R16" s="10">
-        <v>46.532115969886277</v>
+        <v>48.272750708945608</v>
       </c>
       <c r="S16" s="6">
-        <v>0.13357429718875499</v>
+        <v>0.12608165997322621</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3">
         <v>46248</v>
       </c>
       <c r="C17" s="4">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="D17" s="4">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E17" s="5">
-        <v>4.6647230320699708E-2</v>
+        <v>2.3529411764705879E-2</v>
       </c>
       <c r="F17" s="4">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G17" s="6">
-        <v>0.24791086350974931</v>
+        <v>0.23563218390804599</v>
       </c>
       <c r="H17" s="7">
-        <v>0.311</v>
+        <v>0.185</v>
       </c>
       <c r="I17" s="6">
-        <v>0.752</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="J17" s="4">
-        <v>156.75</v>
+        <v>156.47999999999999</v>
       </c>
       <c r="K17" s="6">
-        <v>0.28599999999999998</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="L17" s="2">
-        <v>-10.240000000000011</v>
+        <v>-42.52000000000001</v>
       </c>
       <c r="M17" s="6">
-        <v>0.17499999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="N17" s="6">
-        <v>0.29199999999999998</v>
+        <v>0.182</v>
       </c>
       <c r="O17" s="8">
-        <v>8.0267409470752078</v>
+        <v>7.126724137931034</v>
       </c>
       <c r="P17" s="9">
-        <v>15.19792899408284</v>
+        <v>15.066765578635019</v>
       </c>
       <c r="Q17" s="9">
-        <v>2.3568151147098511</v>
+        <v>2.241837629687998</v>
       </c>
       <c r="R17" s="10">
-        <v>49.333333333333343</v>
+        <v>42.497443762781188</v>
       </c>
       <c r="S17" s="6">
-        <v>0.19791780111500071</v>
+        <v>0.20714586466165411</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="B18" s="3">
         <v>46248</v>
       </c>
       <c r="C18" s="4">
-        <v>483</v>
+        <v>354</v>
       </c>
       <c r="D18" s="4">
-        <v>523</v>
+        <v>325</v>
       </c>
       <c r="E18" s="5">
-        <v>-7.6481835564053538E-2</v>
+        <v>8.9230769230769225E-2</v>
       </c>
       <c r="F18" s="4">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G18" s="6">
-        <v>0.15734989648033129</v>
+        <v>0.25988700564971751</v>
       </c>
       <c r="H18" s="7">
-        <v>0.309</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="I18" s="6">
-        <v>0.745</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J18" s="4">
-        <v>212.69</v>
+        <v>169.47</v>
       </c>
       <c r="K18" s="6">
-        <v>0.311</v>
+        <v>0.27</v>
       </c>
       <c r="L18" s="2">
-        <v>-20.580000000000009</v>
+        <v>-13.94999999999999</v>
       </c>
       <c r="M18" s="6">
-        <v>0.25700000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="N18" s="6">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="O18" s="8">
-        <v>11.138095238095239</v>
+        <v>6.7700564971751414</v>
       </c>
       <c r="P18" s="9">
-        <v>16.652586206896551</v>
+        <v>15.61526946107784</v>
       </c>
       <c r="Q18" s="9">
-        <v>2.2961088753852819</v>
+        <v>2.1231444364579479</v>
       </c>
       <c r="R18" s="10">
-        <v>48.511918754995527</v>
+        <v>40.24901162447631</v>
       </c>
       <c r="S18" s="6">
-        <v>0.2011940298507463</v>
+        <v>0.11551238821287201</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3">
         <v>46248</v>
       </c>
       <c r="C19" s="4">
-        <v>303</v>
+        <v>359</v>
       </c>
       <c r="D19" s="4">
-        <v>270</v>
+        <v>343</v>
       </c>
       <c r="E19" s="5">
-        <v>0.1222222222222222</v>
+        <v>4.6647230320699708E-2</v>
       </c>
       <c r="F19" s="4">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="G19" s="6">
-        <v>0.40924092409240931</v>
+        <v>0.24791086350974931</v>
       </c>
       <c r="H19" s="7">
-        <v>0.30599999999999999</v>
+        <v>0.311</v>
       </c>
       <c r="I19" s="6">
-        <v>0.61699999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="J19" s="4">
-        <v>159.24</v>
+        <v>156.75</v>
       </c>
       <c r="K19" s="6">
-        <v>0.31</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="L19" s="2">
-        <v>10.09</v>
+        <v>-10.240000000000011</v>
       </c>
       <c r="M19" s="6">
-        <v>0.28399999999999997</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="N19" s="6">
-        <v>0.39100000000000001</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="O19" s="8">
-        <v>12.28415841584158</v>
+        <v>8.0267409470752078</v>
       </c>
       <c r="P19" s="9">
-        <v>16.982899628252792</v>
+        <v>15.19792899408284</v>
       </c>
       <c r="Q19" s="9">
-        <v>1.9815039763571829</v>
+        <v>2.3568151147098511</v>
       </c>
       <c r="R19" s="10">
-        <v>40.448379804069333</v>
+        <v>49.333333333333343</v>
       </c>
       <c r="S19" s="6">
-        <v>0.15649743828598051</v>
+        <v>0.19791780111500071</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B20" s="3">
         <v>46248</v>
       </c>
       <c r="C20" s="4">
-        <v>457</v>
+        <v>360</v>
       </c>
       <c r="D20" s="4">
-        <v>411</v>
+        <v>325</v>
       </c>
       <c r="E20" s="5">
-        <v>0.1119221411192214</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="F20" s="4">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="G20" s="6">
-        <v>0.2975929978118162</v>
+        <v>0.21111111111111111</v>
       </c>
       <c r="H20" s="7">
-        <v>0.30399999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="I20" s="6">
-        <v>0.79200000000000004</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>191.84</v>
+        <v>168.79</v>
       </c>
       <c r="K20" s="6">
-        <v>0.38</v>
+        <v>0.313</v>
       </c>
       <c r="L20" s="2">
-        <v>-13.12</v>
+        <v>-5.2000000000000171</v>
       </c>
       <c r="M20" s="6">
-        <v>0.20599999999999999</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="N20" s="6">
-        <v>0.13900000000000001</v>
+        <v>0.313</v>
       </c>
       <c r="O20" s="8">
-        <v>7.9354485776805248</v>
+        <v>9.2761111111111116</v>
       </c>
       <c r="P20" s="9">
-        <v>15.57037914691943</v>
+        <v>15.927352941176469</v>
       </c>
       <c r="Q20" s="9">
-        <v>2.5013758012473688</v>
+        <v>2.153878733866708</v>
       </c>
       <c r="R20" s="10">
-        <v>50.312760633861551</v>
+        <v>43.385271639315128</v>
       </c>
       <c r="S20" s="6">
-        <v>0.1167757977621218</v>
+        <v>0.1115502602026842</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3">
         <v>46248</v>
       </c>
       <c r="C21" s="4">
-        <v>582</v>
+        <v>367</v>
       </c>
       <c r="D21" s="4">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="E21" s="5">
-        <v>0.26521739130434779</v>
+        <v>-0.11778846153846149</v>
       </c>
       <c r="F21" s="4">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="G21" s="6">
-        <v>0.23367697594501721</v>
+        <v>0.21798365122615801</v>
       </c>
       <c r="H21" s="7">
-        <v>0.30199999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="I21" s="6">
-        <v>0.77300000000000002</v>
+        <v>0.749</v>
       </c>
       <c r="J21" s="4">
-        <v>244.5</v>
+        <v>165</v>
       </c>
       <c r="K21" s="6">
-        <v>0.32</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="L21" s="2">
-        <v>42.81</v>
+        <v>-7.6100000000000136</v>
       </c>
       <c r="M21" s="6">
-        <v>0.16200000000000001</v>
+        <v>0.193</v>
       </c>
       <c r="N21" s="6">
-        <v>9.9000000000000005E-2</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="O21" s="8">
-        <v>7.0587628865979379</v>
+        <v>8.2119891008174388</v>
       </c>
       <c r="P21" s="9">
-        <v>15.0705565529623</v>
+        <v>16.095845697329381</v>
       </c>
       <c r="Q21" s="9">
-        <v>2.3889493969972819</v>
+        <v>2.265096144165911</v>
       </c>
       <c r="R21" s="10">
-        <v>41.93047034764826</v>
+        <v>45.963636363636361</v>
       </c>
       <c r="S21" s="6">
-        <v>7.3770155379654062E-2</v>
+        <v>0.1101203226232976</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3">
         <v>46248</v>
       </c>
       <c r="C22" s="4">
-        <v>694</v>
+        <v>367</v>
       </c>
       <c r="D22" s="4">
-        <v>616</v>
+        <v>364</v>
       </c>
       <c r="E22" s="5">
-        <v>0.12662337662337661</v>
+        <v>8.241758241758242E-3</v>
       </c>
       <c r="F22" s="4">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="G22" s="6">
-        <v>0.20893371757925069</v>
+        <v>0.20435967302452321</v>
       </c>
       <c r="H22" s="7">
-        <v>0.29899999999999999</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="I22" s="6">
-        <v>0.72799999999999998</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="J22" s="4">
-        <v>272.42</v>
+        <v>154.63</v>
       </c>
       <c r="K22" s="6">
-        <v>0.27700000000000002</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="L22" s="2">
-        <v>-5.2899999999999636</v>
+        <v>-15.31999999999999</v>
       </c>
       <c r="M22" s="6">
-        <v>0.11799999999999999</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="N22" s="6">
-        <v>0.20200000000000001</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="O22" s="8">
-        <v>5.6350144092219017</v>
+        <v>5.6544959128065386</v>
       </c>
       <c r="P22" s="9">
-        <v>13.295833333333331</v>
+        <v>14.86912181303116</v>
       </c>
       <c r="Q22" s="9">
-        <v>2.5559461431156438</v>
+        <v>2.4042848507662709</v>
       </c>
       <c r="R22" s="10">
-        <v>53.652448425225749</v>
+        <v>50.4171247494018</v>
       </c>
       <c r="S22" s="6">
-        <v>0.14011922707962179</v>
+        <v>0.14663673678809649</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="B23" s="3">
         <v>46248</v>
       </c>
       <c r="C23" s="4">
-        <v>791</v>
+        <v>367</v>
       </c>
       <c r="D23" s="4">
-        <v>728</v>
+        <v>324</v>
       </c>
       <c r="E23" s="5">
-        <v>8.6538461538461536E-2</v>
+        <v>0.13271604938271611</v>
       </c>
       <c r="F23" s="4">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="G23" s="6">
-        <v>0.18078381795195961</v>
+        <v>0.27520435967302448</v>
       </c>
       <c r="H23" s="7">
-        <v>0.29599999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="I23" s="6">
-        <v>0.73199999999999998</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="J23" s="4">
-        <v>330.59</v>
+        <v>175.3</v>
       </c>
       <c r="K23" s="6">
-        <v>0.25800000000000001</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="L23" s="2">
-        <v>35.269999999999982</v>
+        <v>19.79000000000002</v>
       </c>
       <c r="M23" s="6">
-        <v>0.16200000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="N23" s="6">
-        <v>0.20200000000000001</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="O23" s="8">
-        <v>6.8276864728192157</v>
+        <v>4.9272479564032698</v>
       </c>
       <c r="P23" s="9">
-        <v>15.7844</v>
+        <v>14.24327485380117</v>
       </c>
       <c r="Q23" s="9">
-        <v>2.4556559750299618</v>
+        <v>2.1878542448045262</v>
       </c>
       <c r="R23" s="10">
-        <v>43.32254454157718</v>
+        <v>39.794637763833428</v>
       </c>
       <c r="S23" s="6">
-        <v>6.8805291153415452E-2</v>
+        <v>9.3709862385321099E-2</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B24" s="3">
         <v>46248</v>
       </c>
       <c r="C24" s="4">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="D24" s="4">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="E24" s="5">
-        <v>7.4270557029177717E-2</v>
+        <v>5.3672316384180789E-2</v>
       </c>
       <c r="F24" s="4">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="G24" s="6">
-        <v>0.26666666666666672</v>
+        <v>0.18230563002680969</v>
       </c>
       <c r="H24" s="7">
-        <v>0.29099999999999998</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="I24" s="6">
-        <v>0.72099999999999997</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="J24" s="4">
-        <v>195.77</v>
+        <v>189.05</v>
       </c>
       <c r="K24" s="6">
-        <v>0.30599999999999999</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="L24" s="2">
-        <v>8.1400000000000148</v>
+        <v>-5.2399999999999807</v>
       </c>
       <c r="M24" s="6">
-        <v>0.153</v>
+        <v>0.11</v>
       </c>
       <c r="N24" s="6">
-        <v>0.17399999999999999</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="O24" s="8">
-        <v>5.8943209876543214</v>
+        <v>4.8037533512064341</v>
       </c>
       <c r="P24" s="9">
-        <v>13.677486910994761</v>
+        <v>16.318571428571431</v>
       </c>
       <c r="Q24" s="9">
-        <v>2.119791724776654</v>
+        <v>2.0080845004045611</v>
       </c>
       <c r="R24" s="10">
-        <v>37.876079072380847</v>
+        <v>41.343559904787092</v>
       </c>
       <c r="S24" s="6">
-        <v>0.1084718826405868</v>
+        <v>0.11757548618219039</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C25" s="4">
+        <v>378</v>
+      </c>
+      <c r="D25" s="4">
+        <v>389</v>
+      </c>
+      <c r="E25" s="5">
+        <v>-2.8277634961439591E-2</v>
+      </c>
+      <c r="F25" s="4">
         <v>89</v>
       </c>
-      <c r="B25" s="3">
-        <v>46248</v>
-      </c>
-      <c r="C25" s="4">
-        <v>550</v>
-      </c>
-      <c r="D25" s="4">
-        <v>480</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0.14583333333333329</v>
-      </c>
-      <c r="F25" s="4">
-        <v>100</v>
-      </c>
       <c r="G25" s="6">
-        <v>0.1818181818181818</v>
+        <v>0.23544973544973541</v>
       </c>
       <c r="H25" s="7">
-        <v>0.28799999999999998</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="I25" s="6">
-        <v>0.76800000000000002</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="J25" s="4">
-        <v>191.88</v>
+        <v>160.33000000000001</v>
       </c>
       <c r="K25" s="6">
-        <v>0.374</v>
+        <v>0.26</v>
       </c>
       <c r="L25" s="2">
-        <v>9.0600000000000023</v>
+        <v>-27.859999999999989</v>
       </c>
       <c r="M25" s="6">
-        <v>0.13500000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="N25" s="6">
-        <v>0.19400000000000001</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="O25" s="8">
-        <v>5.8134545454545457</v>
+        <v>8.299206349206349</v>
       </c>
       <c r="P25" s="9">
-        <v>14.90888468809074</v>
+        <v>13.573579545454541</v>
       </c>
       <c r="Q25" s="9">
-        <v>2.8984332839953759</v>
+        <v>2.3591878110345319</v>
       </c>
       <c r="R25" s="10">
-        <v>61.340421096518661</v>
+        <v>49.722447452129977</v>
       </c>
       <c r="S25" s="6">
-        <v>0.1190637213254036</v>
+        <v>0.15795283492222781</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B26" s="3">
         <v>46248</v>
       </c>
       <c r="C26" s="4">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="D26" s="4">
-        <v>321</v>
+        <v>407</v>
       </c>
       <c r="E26" s="5">
-        <v>2.180685358255452E-2</v>
+        <v>-6.6339066339066333E-2</v>
       </c>
       <c r="F26" s="4">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G26" s="6">
-        <v>0.29878048780487798</v>
+        <v>0.21842105263157899</v>
       </c>
       <c r="H26" s="7">
-        <v>0.28599999999999998</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="I26" s="6">
-        <v>0.73899999999999999</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="J26" s="4">
-        <v>159.82</v>
+        <v>146.08000000000001</v>
       </c>
       <c r="K26" s="6">
-        <v>0.31</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="L26" s="2">
-        <v>-2.7800000000000011</v>
+        <v>-29.669999999999991</v>
       </c>
       <c r="M26" s="6">
-        <v>7.2999999999999995E-2</v>
+        <v>0.184</v>
       </c>
       <c r="N26" s="6">
-        <v>0.104</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="O26" s="8">
-        <v>4.3213414634146341</v>
+        <v>8.0060526315789478</v>
       </c>
       <c r="P26" s="9">
-        <v>12.36440129449838</v>
+        <v>13.18033707865168</v>
       </c>
       <c r="Q26" s="9">
-        <v>2.089501274179101</v>
+        <v>2.6007471222212142</v>
       </c>
       <c r="R26" s="10">
-        <v>42.003503941934682</v>
+        <v>49.274370208105147</v>
       </c>
       <c r="S26" s="6">
-        <v>0.15270642889255209</v>
+        <v>8.62482546774644E-2</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B27" s="3">
         <v>46248</v>
       </c>
       <c r="C27" s="4">
-        <v>405</v>
+        <v>382</v>
       </c>
       <c r="D27" s="4">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="E27" s="5">
-        <v>0.2461538461538462</v>
+        <v>2.6881720430107531E-2</v>
       </c>
       <c r="F27" s="4">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="G27" s="6">
-        <v>0.2839506172839506</v>
+        <v>0.21465968586387429</v>
       </c>
       <c r="H27" s="7">
-        <v>0.28599999999999998</v>
+        <v>0.255</v>
       </c>
       <c r="I27" s="6">
-        <v>0.73199999999999998</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="J27" s="4">
-        <v>172.99</v>
+        <v>196.67</v>
       </c>
       <c r="K27" s="6">
-        <v>0.28199999999999997</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="L27" s="2">
-        <v>13.93000000000001</v>
+        <v>34.009999999999991</v>
       </c>
       <c r="M27" s="6">
-        <v>0.13600000000000001</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="N27" s="6">
-        <v>0.14099999999999999</v>
+        <v>3.9E-2</v>
       </c>
       <c r="O27" s="8">
-        <v>6.3792592592592587</v>
+        <v>4.8062827225130889</v>
       </c>
       <c r="P27" s="9">
-        <v>14.508130081300809</v>
+        <v>15.00376811594203</v>
       </c>
       <c r="Q27" s="9">
-        <v>2.413202647651671</v>
+        <v>2.0470368505379719</v>
       </c>
       <c r="R27" s="10">
-        <v>48.927683681137637</v>
+        <v>33.238419687801901</v>
       </c>
       <c r="S27" s="6">
-        <v>0.16331994328922489</v>
+        <v>6.3539904659387969E-2</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B28" s="3">
         <v>46248</v>
       </c>
       <c r="C28" s="4">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="D28" s="4">
-        <v>396</v>
+        <v>326</v>
       </c>
       <c r="E28" s="5">
-        <v>4.5454545454545463E-2</v>
+        <v>0.17791411042944791</v>
       </c>
       <c r="F28" s="4">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G28" s="6">
-        <v>0.21980676328502419</v>
+        <v>0.30208333333333331</v>
       </c>
       <c r="H28" s="7">
-        <v>0.28399999999999997</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="I28" s="6">
-        <v>0.79</v>
+        <v>0.752</v>
       </c>
       <c r="J28" s="4">
-        <v>166.92</v>
+        <v>169.5</v>
       </c>
       <c r="K28" s="6">
-        <v>0.34200000000000003</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="L28" s="2">
-        <v>-4.6100000000000136</v>
+        <v>7.1999999999999886</v>
       </c>
       <c r="M28" s="6">
-        <v>0.16700000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="N28" s="6">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="O28" s="8">
-        <v>7.9004830917874402</v>
+        <v>5.774739583333333</v>
       </c>
       <c r="P28" s="9">
-        <v>14.889974293059129</v>
+        <v>14.709537572254341</v>
       </c>
       <c r="Q28" s="9">
-        <v>2.5144996338346099</v>
+        <v>2.366865020127825</v>
       </c>
       <c r="R28" s="10">
-        <v>51.395878265037148</v>
+        <v>48.117994100294993</v>
       </c>
       <c r="S28" s="6">
-        <v>0.13605431868516141</v>
+        <v>0.12800760176557141</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B29" s="3">
         <v>46248</v>
       </c>
       <c r="C29" s="4">
-        <v>463</v>
+        <v>390</v>
       </c>
       <c r="D29" s="4">
-        <v>467</v>
+        <v>426</v>
       </c>
       <c r="E29" s="5">
-        <v>-8.5653104925053538E-3</v>
+        <v>-8.4507042253521125E-2</v>
       </c>
       <c r="F29" s="4">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G29" s="6">
-        <v>0.16846652267818571</v>
+        <v>0.241025641025641</v>
       </c>
       <c r="H29" s="7">
-        <v>0.28000000000000003</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="I29" s="6">
-        <v>0.78600000000000003</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="J29" s="4">
-        <v>196.59</v>
+        <v>167.9</v>
       </c>
       <c r="K29" s="6">
-        <v>0.32500000000000001</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="L29" s="2">
-        <v>-20.609999999999989</v>
+        <v>-38.53</v>
       </c>
       <c r="M29" s="6">
-        <v>0.21</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="N29" s="6">
-        <v>0.11600000000000001</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="O29" s="8">
-        <v>8.5915766738660917</v>
+        <v>10.676410256410261</v>
       </c>
       <c r="P29" s="9">
-        <v>14.035681818181819</v>
+        <v>16.845161290322579</v>
       </c>
       <c r="Q29" s="9">
-        <v>2.4141662557437962</v>
+        <v>2.356835715437275</v>
       </c>
       <c r="R29" s="10">
-        <v>42.519965410244673</v>
+        <v>50.160810005955923</v>
       </c>
       <c r="S29" s="6">
-        <v>6.6618316950371612E-2</v>
+        <v>0.19933333333333331</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B30" s="3">
         <v>46248</v>
       </c>
       <c r="C30" s="4">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="D30" s="4">
-        <v>473</v>
+        <v>272</v>
       </c>
       <c r="E30" s="5">
-        <v>-8.2452431289640596E-2</v>
+        <v>0.4375</v>
       </c>
       <c r="F30" s="4">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="G30" s="6">
-        <v>0.25115207373271892</v>
+        <v>0.32992327365728902</v>
       </c>
       <c r="H30" s="7">
-        <v>0.27800000000000002</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="I30" s="6">
-        <v>0.79900000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="J30" s="4">
-        <v>179.42</v>
+        <v>168.01</v>
       </c>
       <c r="K30" s="6">
-        <v>0.33700000000000002</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="L30" s="2">
-        <v>-25.210000000000012</v>
+        <v>20.829999999999981</v>
       </c>
       <c r="M30" s="6">
-        <v>5.0999999999999997E-2</v>
+        <v>0.161</v>
       </c>
       <c r="N30" s="6">
-        <v>4.5999999999999999E-2</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="O30" s="8">
-        <v>2.84331797235023</v>
+        <v>7.0583120204603587</v>
       </c>
       <c r="P30" s="9">
-        <v>15.17658536585366</v>
+        <v>15.44393530997305</v>
       </c>
       <c r="Q30" s="9">
-        <v>2.4867520613881262</v>
+        <v>2.3448410433080782</v>
       </c>
       <c r="R30" s="10">
-        <v>50.629807156392822</v>
+        <v>45.693708707815013</v>
       </c>
       <c r="S30" s="6">
-        <v>0.13521466314398939</v>
+        <v>0.1199960825280752</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B31" s="3">
         <v>46248</v>
       </c>
       <c r="C31" s="4">
-        <v>286</v>
+        <v>397</v>
       </c>
       <c r="D31" s="4">
-        <v>313</v>
+        <v>414</v>
       </c>
       <c r="E31" s="5">
-        <v>-8.6261980830670923E-2</v>
+        <v>-4.1062801932367152E-2</v>
       </c>
       <c r="F31" s="4">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G31" s="6">
-        <v>0.2937062937062937</v>
+        <v>0.22166246851385391</v>
       </c>
       <c r="H31" s="7">
-        <v>0.27700000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="I31" s="6">
-        <v>0.71299999999999997</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="J31" s="4">
-        <v>155.75</v>
+        <v>159.78</v>
       </c>
       <c r="K31" s="6">
-        <v>0.27600000000000002</v>
+        <v>0.316</v>
       </c>
       <c r="L31" s="2">
-        <v>-7.6399999999999864</v>
+        <v>-7.9199999999999866</v>
       </c>
       <c r="M31" s="6">
-        <v>0.17799999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="N31" s="6">
-        <v>0.24199999999999999</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="O31" s="8">
-        <v>6.668881118881119</v>
+        <v>8.5012594458438286</v>
       </c>
       <c r="P31" s="9">
-        <v>17.631297709923661</v>
+        <v>15.005804749340371</v>
       </c>
       <c r="Q31" s="9">
-        <v>1.84400417772089</v>
+        <v>2.5309686194965959</v>
       </c>
       <c r="R31" s="10">
-        <v>37.06581059390048</v>
+        <v>53.648767054700222</v>
       </c>
       <c r="S31" s="6">
-        <v>9.8813884528170248E-2</v>
+        <v>0.17672240411599621</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="B32" s="3">
         <v>46248</v>
       </c>
       <c r="C32" s="4">
-        <v>551</v>
+        <v>400</v>
       </c>
       <c r="D32" s="4">
-        <v>516</v>
+        <v>394</v>
       </c>
       <c r="E32" s="5">
-        <v>6.7829457364341081E-2</v>
+        <v>1.522842639593909E-2</v>
       </c>
       <c r="F32" s="4">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="G32" s="6">
-        <v>0.29219600725952821</v>
+        <v>0.27</v>
       </c>
       <c r="H32" s="7">
-        <v>0.27400000000000002</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="I32" s="6">
-        <v>0.752</v>
+        <v>0.746</v>
       </c>
       <c r="J32" s="4">
-        <v>219.51</v>
+        <v>169.09</v>
       </c>
       <c r="K32" s="6">
-        <v>0.32300000000000001</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="L32" s="2">
-        <v>22.259999999999991</v>
+        <v>-9.0799999999999841</v>
       </c>
       <c r="M32" s="6">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="N32" s="6">
-        <v>0.32300000000000001</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="O32" s="8">
-        <v>8.2709618874773145</v>
+        <v>6.2029999999999994</v>
       </c>
       <c r="P32" s="9">
-        <v>15.91257035647279</v>
+        <v>13.972251308900519</v>
       </c>
       <c r="Q32" s="9">
-        <v>2.5414995211359841</v>
+        <v>2.401135144066163</v>
       </c>
       <c r="R32" s="10">
-        <v>51.423625347364577</v>
+        <v>47.980365485835947</v>
       </c>
       <c r="S32" s="6">
-        <v>0.1981728636081285</v>
+        <v>0.20814306893995549</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B33" s="3">
         <v>46248</v>
       </c>
       <c r="C33" s="4">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="D33" s="4">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="E33" s="5">
-        <v>-6.6339066339066333E-2</v>
+        <v>7.4270557029177717E-2</v>
       </c>
       <c r="F33" s="4">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="G33" s="6">
-        <v>0.21842105263157899</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="H33" s="7">
-        <v>0.27300000000000002</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="I33" s="6">
-        <v>0.68500000000000005</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="J33" s="4">
-        <v>146.08000000000001</v>
+        <v>195.77</v>
       </c>
       <c r="K33" s="6">
-        <v>0.27100000000000002</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="L33" s="2">
-        <v>-29.669999999999991</v>
+        <v>8.1400000000000148</v>
       </c>
       <c r="M33" s="6">
-        <v>0.184</v>
+        <v>0.153</v>
       </c>
       <c r="N33" s="6">
-        <v>0.34799999999999998</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="O33" s="8">
-        <v>8.0060526315789478</v>
+        <v>5.8943209876543214</v>
       </c>
       <c r="P33" s="9">
-        <v>13.18033707865168</v>
+        <v>13.677486910994761</v>
       </c>
       <c r="Q33" s="9">
-        <v>2.6007471222212142</v>
+        <v>2.119791724776654</v>
       </c>
       <c r="R33" s="10">
-        <v>49.274370208105147</v>
+        <v>37.876079072380847</v>
       </c>
       <c r="S33" s="6">
-        <v>8.62482546774644E-2</v>
+        <v>0.1084718826405868</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="B34" s="3">
         <v>46248</v>
       </c>
       <c r="C34" s="4">
-        <v>631</v>
+        <v>405</v>
       </c>
       <c r="D34" s="4">
-        <v>593</v>
+        <v>325</v>
       </c>
       <c r="E34" s="5">
-        <v>6.4080944350758853E-2</v>
+        <v>0.2461538461538462</v>
       </c>
       <c r="F34" s="4">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="G34" s="6">
-        <v>0.21236133122028519</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="H34" s="7">
-        <v>0.26700000000000002</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="I34" s="6">
-        <v>0.69199999999999995</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="J34" s="4">
-        <v>230.51</v>
+        <v>172.99</v>
       </c>
       <c r="K34" s="6">
-        <v>0.26</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="L34" s="2">
-        <v>10.259999999999989</v>
+        <v>13.93000000000001</v>
       </c>
       <c r="M34" s="6">
-        <v>0.192</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="N34" s="6">
-        <v>0.36199999999999999</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="O34" s="8">
-        <v>8.6516640253565757</v>
+        <v>6.3792592592592587</v>
       </c>
       <c r="P34" s="9">
-        <v>12.87091836734694</v>
+        <v>14.508130081300809</v>
       </c>
       <c r="Q34" s="9">
-        <v>2.8485154653378948</v>
+        <v>2.413202647651671</v>
       </c>
       <c r="R34" s="10">
-        <v>53.815452691857189</v>
+        <v>48.927683681137637</v>
       </c>
       <c r="S34" s="6">
-        <v>8.802745256358499E-2</v>
+        <v>0.16331994328922489</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B35" s="3">
         <v>46248</v>
       </c>
       <c r="C35" s="4">
-        <v>528</v>
+        <v>405</v>
       </c>
       <c r="D35" s="4">
-        <v>558</v>
+        <v>348</v>
       </c>
       <c r="E35" s="5">
-        <v>-5.3763440860215048E-2</v>
+        <v>0.16379310344827591</v>
       </c>
       <c r="F35" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G35" s="6">
-        <v>0.19886363636363641</v>
+        <v>0.25432098765432098</v>
       </c>
       <c r="H35" s="7">
-        <v>0.26700000000000002</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="I35" s="6">
-        <v>0.79700000000000004</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="J35" s="4">
-        <v>182.64</v>
+        <v>164.09</v>
       </c>
       <c r="K35" s="6">
-        <v>0.29699999999999999</v>
+        <v>0.254</v>
       </c>
       <c r="L35" s="2">
-        <v>-16.44000000000003</v>
+        <v>9.7199999999999989</v>
       </c>
       <c r="M35" s="6">
-        <v>0.23899999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="N35" s="6">
-        <v>0.32900000000000001</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="O35" s="8">
-        <v>10.14488636363636</v>
+        <v>4.8708641975308646</v>
       </c>
       <c r="P35" s="9">
-        <v>14.38198757763975</v>
+        <v>14.19922279792746</v>
       </c>
       <c r="Q35" s="9">
-        <v>2.993477918626374</v>
+        <v>2.5042798962565782</v>
       </c>
       <c r="R35" s="10">
-        <v>60.731493648707847</v>
+        <v>51.965384849777557</v>
       </c>
       <c r="S35" s="6">
-        <v>0.12324918566775241</v>
+        <v>9.461728395061729E-2</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B36" s="3">
         <v>46248</v>
       </c>
       <c r="C36" s="4">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="D36" s="4">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="E36" s="5">
-        <v>0.1132530120481928</v>
+        <v>5.1150895140664961E-2</v>
       </c>
       <c r="F36" s="4">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G36" s="6">
-        <v>0.20995670995671001</v>
+        <v>0.20924574209245739</v>
       </c>
       <c r="H36" s="7">
-        <v>0.26500000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="I36" s="6">
-        <v>0.78600000000000003</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="J36" s="4">
-        <v>185.55</v>
+        <v>163.25</v>
       </c>
       <c r="K36" s="6">
-        <v>0.311</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="L36" s="2">
-        <v>6.6300000000000239</v>
+        <v>9.0000000000003411E-2</v>
       </c>
       <c r="M36" s="6">
-        <v>0.08</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="N36" s="6">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="O36" s="8">
-        <v>3.5179653679653682</v>
+        <v>5.7153284671532836</v>
       </c>
       <c r="P36" s="9">
-        <v>15.64331797235023</v>
+        <v>13.94230769230769</v>
       </c>
       <c r="Q36" s="9">
-        <v>2.5313012513751172</v>
+        <v>2.5496718796351558</v>
       </c>
       <c r="R36" s="10">
-        <v>53.424952842899494</v>
+        <v>54.603369065849932</v>
       </c>
       <c r="S36" s="6">
-        <v>0.1050379132544738</v>
+        <v>0.15757606490872211</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="B37" s="3">
         <v>46248</v>
       </c>
       <c r="C37" s="4">
-        <v>873</v>
+        <v>413</v>
       </c>
       <c r="D37" s="4">
-        <v>765</v>
+        <v>379</v>
       </c>
       <c r="E37" s="5">
-        <v>0.14117647058823529</v>
+        <v>8.9709762532981532E-2</v>
       </c>
       <c r="F37" s="4">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="G37" s="6">
-        <v>0.18556701030927841</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="H37" s="7">
-        <v>0.26300000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="I37" s="6">
-        <v>0.80300000000000005</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="J37" s="4">
-        <v>313.42</v>
+        <v>187.29</v>
       </c>
       <c r="K37" s="6">
-        <v>0.29899999999999999</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="L37" s="2">
-        <v>36.610000000000007</v>
+        <v>14.919999999999989</v>
       </c>
       <c r="M37" s="6">
-        <v>0.16200000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="N37" s="6">
-        <v>0.104</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="O37" s="8">
-        <v>7.5775486827033216</v>
+        <v>4.8142857142857141</v>
       </c>
       <c r="P37" s="9">
-        <v>15.26602641056423</v>
+        <v>15.094736842105259</v>
       </c>
       <c r="Q37" s="9">
-        <v>2.8232961837954131</v>
+        <v>2.2413260746773229</v>
       </c>
       <c r="R37" s="10">
-        <v>56.891710803394801</v>
+        <v>46.532115969886277</v>
       </c>
       <c r="S37" s="6">
-        <v>0.17161036479118649</v>
+        <v>0.13357429718875499</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B38" s="3">
         <v>46248</v>
       </c>
       <c r="C38" s="4">
-        <v>291</v>
+        <v>414</v>
       </c>
       <c r="D38" s="4">
-        <v>286</v>
+        <v>400</v>
       </c>
       <c r="E38" s="5">
-        <v>1.748251748251748E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="F38" s="4">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G38" s="6">
-        <v>0.23024054982817871</v>
+        <v>0.21980676328502419</v>
       </c>
       <c r="H38" s="7">
-        <v>0.26200000000000001</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="I38" s="6">
-        <v>0.71799999999999997</v>
+        <v>0.71</v>
       </c>
       <c r="J38" s="4">
-        <v>140.15</v>
+        <v>166.39</v>
       </c>
       <c r="K38" s="6">
-        <v>0.28599999999999998</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="L38" s="2">
-        <v>-9.3199999999999932</v>
+        <v>-25.54000000000002</v>
       </c>
       <c r="M38" s="6">
-        <v>0.20300000000000001</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="N38" s="6">
-        <v>0.23499999999999999</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="O38" s="8">
-        <v>8.5120274914089347</v>
+        <v>8</v>
       </c>
       <c r="P38" s="9">
-        <v>15.806115107913669</v>
+        <v>15.4032</v>
       </c>
       <c r="Q38" s="9">
-        <v>2.125144580278056</v>
+        <v>2.5772724619270519</v>
       </c>
       <c r="R38" s="10">
-        <v>43.503389225829473</v>
+        <v>51.475449245747953</v>
       </c>
       <c r="S38" s="6">
-        <v>0.32671313760866</v>
+        <v>0.1137486738182247</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B39" s="3">
         <v>46248</v>
       </c>
       <c r="C39" s="4">
-        <v>515</v>
+        <v>414</v>
       </c>
       <c r="D39" s="4">
-        <v>467</v>
+        <v>396</v>
       </c>
       <c r="E39" s="5">
-        <v>0.1027837259100642</v>
+        <v>4.5454545454545463E-2</v>
       </c>
       <c r="F39" s="4">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G39" s="6">
-        <v>0.2174757281553398</v>
+        <v>0.21980676328502419</v>
       </c>
       <c r="H39" s="7">
-        <v>0.26100000000000001</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="I39" s="6">
-        <v>0.60599999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="J39" s="4">
-        <v>233.47</v>
+        <v>166.92</v>
       </c>
       <c r="K39" s="6">
-        <v>0.29499999999999998</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="L39" s="2">
-        <v>-23.900000000000009</v>
+        <v>-4.6100000000000136</v>
       </c>
       <c r="M39" s="6">
-        <v>0.115</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="N39" s="6">
-        <v>8.7999999999999995E-2</v>
+        <v>0.23</v>
       </c>
       <c r="O39" s="8">
-        <v>5.4040776699029127</v>
+        <v>7.9004830917874402</v>
       </c>
       <c r="P39" s="9">
-        <v>15.237909836065571</v>
+        <v>14.889974293059129</v>
       </c>
       <c r="Q39" s="9">
-        <v>2.212808375265805</v>
+        <v>2.5144996338346099</v>
       </c>
       <c r="R39" s="10">
-        <v>45.397695635413541</v>
+        <v>51.395878265037148</v>
       </c>
       <c r="S39" s="6">
-        <v>0.14903858854608931</v>
+        <v>0.13605431868516141</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B40" s="3">
         <v>46248</v>
       </c>
       <c r="C40" s="4">
-        <v>669</v>
+        <v>416</v>
       </c>
       <c r="D40" s="4">
-        <v>604</v>
+        <v>459</v>
       </c>
       <c r="E40" s="5">
-        <v>0.10761589403973509</v>
+        <v>-9.3681917211328972E-2</v>
       </c>
       <c r="F40" s="4">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G40" s="6">
-        <v>0.1599402092675635</v>
+        <v>0.27163461538461542</v>
       </c>
       <c r="H40" s="7">
-        <v>0.25900000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="I40" s="6">
         <v>0.78400000000000003</v>
       </c>
       <c r="J40" s="4">
-        <v>244.58</v>
+        <v>222.84</v>
       </c>
       <c r="K40" s="6">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="L40" s="2">
-        <v>38.230000000000018</v>
+        <v>-4.6800000000000068</v>
       </c>
       <c r="M40" s="6">
-        <v>9.4E-2</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="N40" s="6">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="O40" s="8">
-        <v>5.1059790732436472</v>
+        <v>6.867548076923077</v>
       </c>
       <c r="P40" s="9">
-        <v>13.595911949685529</v>
+        <v>17.479015544041449</v>
       </c>
       <c r="Q40" s="9">
-        <v>2.7572901950398681</v>
+        <v>1.912861284929207</v>
       </c>
       <c r="R40" s="10">
-        <v>55.556464142611823</v>
+        <v>34.356488960689283</v>
       </c>
       <c r="S40" s="6">
-        <v>0.11640344421548431</v>
+        <v>8.1396692045156219E-2</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" s="3">
-        <v>46248</v>
-      </c>
-      <c r="C41" s="4">
-        <v>759</v>
-      </c>
-      <c r="D41" s="4">
-        <v>853</v>
-      </c>
-      <c r="E41" s="5">
-        <v>-0.1101992966002345</v>
-      </c>
-      <c r="F41" s="4">
-        <v>123</v>
-      </c>
-      <c r="G41" s="6">
-        <v>0.16205533596837951</v>
-      </c>
-      <c r="H41" s="7">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="I41" s="6">
-        <v>0.77600000000000002</v>
-      </c>
-      <c r="J41" s="4">
-        <v>317.83999999999997</v>
-      </c>
-      <c r="K41" s="6">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="L41" s="2">
-        <v>-41.94</v>
-      </c>
-      <c r="M41" s="6">
-        <v>0.124</v>
-      </c>
-      <c r="N41" s="6">
-        <v>0.182</v>
-      </c>
-      <c r="O41" s="8">
-        <v>5.7517786561264828</v>
-      </c>
-      <c r="P41" s="9">
-        <v>14.35020746887967</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>2.43620380166008</v>
-      </c>
-      <c r="R41" s="10">
-        <v>46.054618676063427</v>
-      </c>
-      <c r="S41" s="6">
-        <v>0.1005267123287671</v>
+      <c r="A41" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="12">
+        <v>46248</v>
+      </c>
+      <c r="C41" s="13">
+        <v>424</v>
+      </c>
+      <c r="D41" s="13">
+        <v>421</v>
+      </c>
+      <c r="E41" s="14">
+        <v>7.1258907363420431E-3</v>
+      </c>
+      <c r="F41" s="13">
+        <v>81</v>
+      </c>
+      <c r="G41" s="15">
+        <v>0.19103773584905659</v>
+      </c>
+      <c r="H41" s="16">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I41" s="15">
+        <v>0.746</v>
+      </c>
+      <c r="J41" s="13">
+        <v>209.43</v>
+      </c>
+      <c r="K41" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="L41" s="11">
+        <v>22.56</v>
+      </c>
+      <c r="M41" s="15">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="N41" s="15">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="O41" s="17">
+        <v>9.6146226415094329</v>
+      </c>
+      <c r="P41" s="18">
+        <v>17.747394540942931</v>
+      </c>
+      <c r="Q41" s="18">
+        <v>2.0549539055425869</v>
+      </c>
+      <c r="R41" s="19">
+        <v>40.118416654729501</v>
+      </c>
+      <c r="S41" s="15">
+        <v>0.1239887841546355</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B42" s="3">
         <v>46248</v>
       </c>
       <c r="C42" s="4">
-        <v>354</v>
+        <v>424</v>
       </c>
       <c r="D42" s="4">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="E42" s="5">
-        <v>8.9230769230769225E-2</v>
+        <v>2.415458937198068E-2</v>
       </c>
       <c r="F42" s="4">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G42" s="6">
-        <v>0.25988700564971751</v>
+        <v>0.14858490566037741</v>
       </c>
       <c r="H42" s="7">
-        <v>0.25700000000000001</v>
+        <v>0.246</v>
       </c>
       <c r="I42" s="6">
-        <v>0.69399999999999995</v>
+        <v>0.745</v>
       </c>
       <c r="J42" s="4">
-        <v>169.47</v>
+        <v>173.63</v>
       </c>
       <c r="K42" s="6">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="L42" s="2">
-        <v>-13.94999999999999</v>
+        <v>-1.539999999999992</v>
       </c>
       <c r="M42" s="6">
-        <v>0.15</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="N42" s="6">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="O42" s="8">
-        <v>6.7700564971751414</v>
+        <v>8.964150943396227</v>
       </c>
       <c r="P42" s="9">
-        <v>15.61526946107784</v>
+        <v>15.59140049140049</v>
       </c>
       <c r="Q42" s="9">
-        <v>2.1231444364579479</v>
+        <v>2.4464304119181421</v>
       </c>
       <c r="R42" s="10">
-        <v>40.24901162447631</v>
+        <v>50.469388930484357</v>
       </c>
       <c r="S42" s="6">
-        <v>0.11551238821287201</v>
+        <v>0.121425310966564</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B43" s="3">
         <v>46248</v>
       </c>
       <c r="C43" s="4">
-        <v>504</v>
+        <v>427</v>
       </c>
       <c r="D43" s="4">
-        <v>443</v>
+        <v>401</v>
       </c>
       <c r="E43" s="5">
-        <v>0.13769751693002261</v>
+        <v>6.4837905236907731E-2</v>
       </c>
       <c r="F43" s="4">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="G43" s="6">
-        <v>0.30753968253968261</v>
+        <v>0.22248243559718969</v>
       </c>
       <c r="H43" s="7">
-        <v>0.25600000000000001</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="I43" s="6">
-        <v>0.71499999999999997</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="J43" s="4">
-        <v>235.45</v>
+        <v>171.95</v>
       </c>
       <c r="K43" s="6">
-        <v>0.27100000000000002</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L43" s="2">
-        <v>35.269999999999982</v>
+        <v>27.41</v>
       </c>
       <c r="M43" s="6">
-        <v>0.23799999999999999</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="N43" s="6">
-        <v>0.252</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="O43" s="8">
-        <v>10.75238095238095</v>
+        <v>4.9046838407494153</v>
       </c>
       <c r="P43" s="9">
-        <v>15.80194384449244</v>
+        <v>12.42493827160494</v>
       </c>
       <c r="Q43" s="9">
-        <v>2.1890089062899221</v>
+        <v>2.509309278859432</v>
       </c>
       <c r="R43" s="10">
-        <v>43.457209598640901</v>
+        <v>49.717941261994767</v>
       </c>
       <c r="S43" s="6">
-        <v>0.10663470945020539</v>
+        <v>0.1046787807737397</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="B44" s="3">
         <v>46248</v>
       </c>
       <c r="C44" s="4">
-        <v>641</v>
+        <v>428</v>
       </c>
       <c r="D44" s="4">
-        <v>571</v>
+        <v>444</v>
       </c>
       <c r="E44" s="5">
-        <v>0.1225919439579685</v>
+        <v>-3.6036036036036043E-2</v>
       </c>
       <c r="F44" s="4">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="G44" s="6">
-        <v>0.26677067082683309</v>
+        <v>0.28271028037383178</v>
       </c>
       <c r="H44" s="7">
-        <v>0.25600000000000001</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="I44" s="6">
-        <v>0.79200000000000004</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="J44" s="4">
-        <v>260.98</v>
+        <v>171.99</v>
       </c>
       <c r="K44" s="6">
-        <v>0.35399999999999998</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="L44" s="2">
-        <v>18.900000000000009</v>
+        <v>-37.699999999999989</v>
       </c>
       <c r="M44" s="6">
-        <v>0.17499999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="N44" s="6">
-        <v>0.154</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="O44" s="8">
-        <v>7.6770670826833074</v>
+        <v>8.6852803738317768</v>
       </c>
       <c r="P44" s="9">
-        <v>14.986423841059599</v>
+        <v>15.47164179104478</v>
       </c>
       <c r="Q44" s="9">
-        <v>2.5249317945142371</v>
+        <v>2.525083238363389</v>
       </c>
       <c r="R44" s="10">
-        <v>50.586251820062827</v>
+        <v>51.247165532879819</v>
       </c>
       <c r="S44" s="6">
-        <v>0.13505440986226311</v>
+        <v>0.1469559791241207</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="B45" s="3">
         <v>46248</v>
       </c>
       <c r="C45" s="4">
-        <v>647</v>
+        <v>428</v>
       </c>
       <c r="D45" s="4">
-        <v>537</v>
+        <v>386</v>
       </c>
       <c r="E45" s="5">
-        <v>0.2048417132216015</v>
+        <v>0.1088082901554404</v>
       </c>
       <c r="F45" s="4">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="G45" s="6">
-        <v>0.2395672333848532</v>
+        <v>0.27570093457943923</v>
       </c>
       <c r="H45" s="7">
-        <v>0.255</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="I45" s="6">
-        <v>0.70699999999999996</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="J45" s="4">
-        <v>248.49</v>
+        <v>189.23</v>
       </c>
       <c r="K45" s="6">
-        <v>0.32100000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="L45" s="2">
-        <v>60.69</v>
+        <v>22.349999999999991</v>
       </c>
       <c r="M45" s="6">
-        <v>0.318</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="N45" s="6">
-        <v>0.316</v>
+        <v>0.19</v>
       </c>
       <c r="O45" s="8">
-        <v>13.94899536321484</v>
+        <v>6.8899532710280376</v>
       </c>
       <c r="P45" s="9">
-        <v>16.701482701812189</v>
+        <v>15.1953431372549</v>
       </c>
       <c r="Q45" s="9">
-        <v>2.672606342323355</v>
+        <v>2.3039136310839532</v>
       </c>
       <c r="R45" s="10">
-        <v>53.205360376675117</v>
+        <v>46.218887068646623</v>
       </c>
       <c r="S45" s="6">
-        <v>0.14885714285714291</v>
+        <v>0.1470706608735422</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B46" s="3">
         <v>46248</v>
       </c>
       <c r="C46" s="4">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="D46" s="4">
-        <v>372</v>
+        <v>473</v>
       </c>
       <c r="E46" s="5">
-        <v>2.6881720430107531E-2</v>
+        <v>-8.2452431289640596E-2</v>
       </c>
       <c r="F46" s="4">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="G46" s="6">
-        <v>0.21465968586387429</v>
+        <v>0.25115207373271892</v>
       </c>
       <c r="H46" s="7">
-        <v>0.255</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="I46" s="6">
-        <v>0.81399999999999995</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="J46" s="4">
-        <v>196.67</v>
+        <v>179.42</v>
       </c>
       <c r="K46" s="6">
-        <v>0.40300000000000002</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="L46" s="2">
-        <v>34.009999999999991</v>
+        <v>-25.210000000000012</v>
       </c>
       <c r="M46" s="6">
-        <v>9.9000000000000005E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="N46" s="6">
-        <v>3.9E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="O46" s="8">
-        <v>4.8062827225130889</v>
+        <v>2.84331797235023</v>
       </c>
       <c r="P46" s="9">
-        <v>15.00376811594203</v>
+        <v>15.17658536585366</v>
       </c>
       <c r="Q46" s="9">
-        <v>2.0470368505379719</v>
+        <v>2.4867520613881262</v>
       </c>
       <c r="R46" s="10">
-        <v>33.238419687801901</v>
+        <v>50.629807156392822</v>
       </c>
       <c r="S46" s="6">
-        <v>6.3539904659387969E-2</v>
+        <v>0.13521466314398939</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B47" s="3">
         <v>46248</v>
       </c>
       <c r="C47" s="4">
-        <v>544</v>
+        <v>457</v>
       </c>
       <c r="D47" s="4">
-        <v>584</v>
+        <v>411</v>
       </c>
       <c r="E47" s="5">
-        <v>-6.8493150684931503E-2</v>
+        <v>0.1119221411192214</v>
       </c>
       <c r="F47" s="4">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="G47" s="6">
-        <v>0.2095588235294118</v>
+        <v>0.2975929978118162</v>
       </c>
       <c r="H47" s="7">
-        <v>0.254</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="I47" s="6">
-        <v>0.78300000000000003</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="J47" s="4">
-        <v>235.46</v>
+        <v>191.84</v>
       </c>
       <c r="K47" s="6">
-        <v>0.30299999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="L47" s="2">
-        <v>-9.3899999999999864</v>
+        <v>-13.12</v>
       </c>
       <c r="M47" s="6">
-        <v>0.182</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="N47" s="6">
-        <v>0.26100000000000001</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="O47" s="8">
-        <v>7.1389705882352938</v>
+        <v>7.9354485776805248</v>
       </c>
       <c r="P47" s="9">
-        <v>15.324427480916031</v>
+        <v>15.57037914691943</v>
       </c>
       <c r="Q47" s="9">
-        <v>2.3389575204870572</v>
+        <v>2.5013758012473688</v>
       </c>
       <c r="R47" s="10">
-        <v>49.605028454939273</v>
+        <v>50.312760633861551</v>
       </c>
       <c r="S47" s="6">
-        <v>0.15082388316151199</v>
+        <v>0.1167757977621218</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="B48" s="3">
         <v>46248</v>
       </c>
       <c r="C48" s="4">
-        <v>936</v>
+        <v>462</v>
       </c>
       <c r="D48" s="4">
-        <v>831</v>
+        <v>496</v>
       </c>
       <c r="E48" s="5">
-        <v>0.1263537906137184</v>
+        <v>-6.8548387096774188E-2</v>
       </c>
       <c r="F48" s="4">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="G48" s="6">
-        <v>0.25961538461538458</v>
+        <v>0.145021645021645</v>
       </c>
       <c r="H48" s="7">
-        <v>0.248</v>
+        <v>0.223</v>
       </c>
       <c r="I48" s="6">
-        <v>0.77700000000000002</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="J48" s="4">
-        <v>336.22</v>
+        <v>195.6</v>
       </c>
       <c r="K48" s="6">
-        <v>0.29599999999999999</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="L48" s="2">
-        <v>40.470000000000027</v>
+        <v>6.6800000000000068</v>
       </c>
       <c r="M48" s="6">
-        <v>0.109</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="N48" s="6">
-        <v>9.5000000000000001E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="O48" s="8">
-        <v>5.8522435897435896</v>
+        <v>3.2865800865800869</v>
       </c>
       <c r="P48" s="9">
-        <v>15.124776785714291</v>
+        <v>12.07090909090909</v>
       </c>
       <c r="Q48" s="9">
-        <v>2.8349842710218152</v>
+        <v>2.344890898142713</v>
       </c>
       <c r="R48" s="10">
-        <v>56.843733269882811</v>
+        <v>47.816973415132928</v>
       </c>
       <c r="S48" s="6">
-        <v>0.1123464096789399</v>
+        <v>0.13657436116753979</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B49" s="3">
         <v>46248</v>
       </c>
       <c r="C49" s="4">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="D49" s="4">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E49" s="5">
-        <v>2.415458937198068E-2</v>
+        <v>0.1132530120481928</v>
       </c>
       <c r="F49" s="4">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="G49" s="6">
-        <v>0.14858490566037741</v>
+        <v>0.20995670995671001</v>
       </c>
       <c r="H49" s="7">
-        <v>0.246</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="I49" s="6">
-        <v>0.745</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="J49" s="4">
-        <v>173.63</v>
+        <v>185.55</v>
       </c>
       <c r="K49" s="6">
-        <v>0.26</v>
+        <v>0.311</v>
       </c>
       <c r="L49" s="2">
-        <v>-1.539999999999992</v>
+        <v>6.6300000000000239</v>
       </c>
       <c r="M49" s="6">
-        <v>0.23799999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N49" s="6">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="O49" s="8">
-        <v>8.964150943396227</v>
+        <v>3.5179653679653682</v>
       </c>
       <c r="P49" s="9">
-        <v>15.59140049140049</v>
+        <v>15.64331797235023</v>
       </c>
       <c r="Q49" s="9">
-        <v>2.4464304119181421</v>
+        <v>2.5313012513751172</v>
       </c>
       <c r="R49" s="10">
-        <v>50.469388930484357</v>
+        <v>53.424952842899494</v>
       </c>
       <c r="S49" s="6">
-        <v>0.121425310966564</v>
+        <v>0.1050379132544738</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="B50" s="3">
         <v>46248</v>
       </c>
       <c r="C50" s="4">
-        <v>346</v>
+        <v>463</v>
       </c>
       <c r="D50" s="4">
-        <v>332</v>
+        <v>467</v>
       </c>
       <c r="E50" s="5">
-        <v>4.2168674698795178E-2</v>
+        <v>-8.5653104925053538E-3</v>
       </c>
       <c r="F50" s="4">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G50" s="6">
-        <v>0.2774566473988439</v>
+        <v>0.16846652267818571</v>
       </c>
       <c r="H50" s="7">
-        <v>0.24399999999999999</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I50" s="6">
-        <v>0.81200000000000006</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="J50" s="4">
-        <v>155.16</v>
+        <v>196.59</v>
       </c>
       <c r="K50" s="6">
-        <v>0.307</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="L50" s="2">
-        <v>1.359999999999985</v>
+        <v>-20.609999999999989</v>
       </c>
       <c r="M50" s="6">
-        <v>4.9000000000000002E-2</v>
+        <v>0.21</v>
       </c>
       <c r="N50" s="6">
-        <v>5.5E-2</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="O50" s="8">
-        <v>2.9710982658959542</v>
+        <v>8.5915766738660917</v>
       </c>
       <c r="P50" s="9">
-        <v>12.665060240963861</v>
+        <v>14.035681818181819</v>
       </c>
       <c r="Q50" s="9">
-        <v>2.2704164949244312</v>
+        <v>2.4141662557437962</v>
       </c>
       <c r="R50" s="10">
-        <v>48.272750708945608</v>
+        <v>42.519965410244673</v>
       </c>
       <c r="S50" s="6">
-        <v>0.12608165997322621</v>
+        <v>6.6618316950371612E-2</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B51" s="3">
         <v>46248</v>
       </c>
       <c r="C51" s="4">
-        <v>318</v>
+        <v>465</v>
       </c>
       <c r="D51" s="4">
-        <v>260</v>
+        <v>450</v>
       </c>
       <c r="E51" s="5">
-        <v>0.22307692307692309</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="F51" s="4">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G51" s="6">
-        <v>0.25786163522012578</v>
+        <v>0.20645161290322581</v>
       </c>
       <c r="H51" s="7">
-        <v>0.24199999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="I51" s="6">
-        <v>0.755</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="J51" s="4">
-        <v>175.38</v>
+        <v>196.83</v>
       </c>
       <c r="K51" s="6">
-        <v>0.315</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="L51" s="2">
-        <v>19.039999999999988</v>
+        <v>15.03</v>
       </c>
       <c r="M51" s="6">
-        <v>0.129</v>
+        <v>0.247</v>
       </c>
       <c r="N51" s="6">
-        <v>0.22600000000000001</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="O51" s="8">
-        <v>5.2062893081761006</v>
+        <v>10.0705376344086</v>
       </c>
       <c r="P51" s="9">
-        <v>16.116107382550339</v>
+        <v>16.278571428571428</v>
       </c>
       <c r="Q51" s="9">
-        <v>1.850250752796174</v>
+        <v>2.4286590816083269</v>
       </c>
       <c r="R51" s="10">
-        <v>39.23480442467784</v>
+        <v>48.51394604481024</v>
       </c>
       <c r="S51" s="6">
-        <v>0.11128033716029651</v>
+        <v>0.11919049115090589</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="B52" s="3">
         <v>46248</v>
       </c>
       <c r="C52" s="4">
-        <v>373</v>
+        <v>471</v>
       </c>
       <c r="D52" s="4">
-        <v>354</v>
+        <v>494</v>
       </c>
       <c r="E52" s="5">
-        <v>5.3672316384180789E-2</v>
+        <v>-4.6558704453441298E-2</v>
       </c>
       <c r="F52" s="4">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="G52" s="6">
-        <v>0.18230563002680969</v>
+        <v>0.20806794055201699</v>
       </c>
       <c r="H52" s="7">
-        <v>0.23400000000000001</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="I52" s="6">
-        <v>0.69699999999999995</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="J52" s="4">
-        <v>189.05</v>
+        <v>197.03</v>
       </c>
       <c r="K52" s="6">
-        <v>0.28899999999999998</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="L52" s="2">
-        <v>-5.2399999999999807</v>
+        <v>-22.150000000000009</v>
       </c>
       <c r="M52" s="6">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="N52" s="6">
-        <v>0.13200000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O52" s="8">
-        <v>4.8037533512064341</v>
+        <v>5.1968152866242026</v>
       </c>
       <c r="P52" s="9">
-        <v>16.318571428571431</v>
+        <v>14.0718820861678</v>
       </c>
       <c r="Q52" s="9">
-        <v>2.0080845004045611</v>
+        <v>2.415816460600329</v>
       </c>
       <c r="R52" s="10">
-        <v>41.343559904787092</v>
+        <v>46.348271836776128</v>
       </c>
       <c r="S52" s="6">
-        <v>0.11757548618219039</v>
+        <v>7.5732351000659781E-2</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B53" s="3">
         <v>46248</v>
       </c>
       <c r="C53" s="4">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="D53" s="4">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="E53" s="5">
-        <v>3.5000000000000003E-2</v>
+        <v>3.4858387799564267E-2</v>
       </c>
       <c r="F53" s="4">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G53" s="6">
-        <v>0.21980676328502419</v>
+        <v>0.2063157894736842</v>
       </c>
       <c r="H53" s="7">
-        <v>0.22900000000000001</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="I53" s="6">
-        <v>0.71</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J53" s="4">
-        <v>166.39</v>
+        <v>186.08</v>
       </c>
       <c r="K53" s="6">
-        <v>0.27600000000000002</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="L53" s="2">
-        <v>-25.54000000000002</v>
+        <v>-10.16</v>
       </c>
       <c r="M53" s="6">
-        <v>0.19600000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="N53" s="6">
-        <v>0.33600000000000002</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="O53" s="8">
-        <v>8</v>
+        <v>4.530736842105263</v>
       </c>
       <c r="P53" s="9">
-        <v>15.4032</v>
+        <v>13.92668161434978</v>
       </c>
       <c r="Q53" s="9">
-        <v>2.5772724619270519</v>
+        <v>2.5823461963367609</v>
       </c>
       <c r="R53" s="10">
-        <v>51.475449245747953</v>
+        <v>53.659716251074798</v>
       </c>
       <c r="S53" s="6">
-        <v>0.1137486738182247</v>
+        <v>0.20070305458187279</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B54" s="3">
         <v>46248</v>
       </c>
       <c r="C54" s="4">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D54" s="4">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="E54" s="5">
-        <v>3.4858387799564267E-2</v>
+        <v>7.1748878923766815E-2</v>
       </c>
       <c r="F54" s="4">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G54" s="6">
-        <v>0.2063157894736842</v>
+        <v>0.17573221757322169</v>
       </c>
       <c r="H54" s="7">
-        <v>0.22800000000000001</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="I54" s="6">
-        <v>0.69399999999999995</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="J54" s="4">
-        <v>186.08</v>
+        <v>202.09</v>
       </c>
       <c r="K54" s="6">
-        <v>0.27200000000000002</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L54" s="2">
-        <v>-10.16</v>
+        <v>-18.849999999999991</v>
       </c>
       <c r="M54" s="6">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="N54" s="6">
-        <v>0.16400000000000001</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="O54" s="8">
-        <v>4.530736842105263</v>
+        <v>5.4619246861924688</v>
       </c>
       <c r="P54" s="9">
-        <v>13.92668161434978</v>
+        <v>14.83728070175439</v>
       </c>
       <c r="Q54" s="9">
-        <v>2.5823461963367609</v>
+        <v>2.4029885086727472</v>
       </c>
       <c r="R54" s="10">
-        <v>53.659716251074798</v>
+        <v>50.635855311989708</v>
       </c>
       <c r="S54" s="6">
-        <v>0.20070305458187279</v>
+        <v>0.1009469363822926</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B55" s="3">
         <v>46248</v>
       </c>
       <c r="C55" s="4">
-        <v>632</v>
+        <v>479</v>
       </c>
       <c r="D55" s="4">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E55" s="5">
-        <v>2.4311183144246351E-2</v>
+        <v>-0.22491909385113271</v>
       </c>
       <c r="F55" s="4">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="G55" s="6">
-        <v>0.19778481012658231</v>
+        <v>0.23799582463465549</v>
       </c>
       <c r="H55" s="7">
-        <v>0.22500000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I55" s="6">
-        <v>0.72899999999999998</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="J55" s="4">
-        <v>212.13</v>
+        <v>191.07</v>
       </c>
       <c r="K55" s="6">
-        <v>0.27800000000000002</v>
+        <v>0.311</v>
       </c>
       <c r="L55" s="2">
-        <v>-29.63</v>
+        <v>-29.28</v>
       </c>
       <c r="M55" s="6">
-        <v>0.13400000000000001</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="N55" s="6">
-        <v>0.22600000000000001</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="O55" s="8">
-        <v>6.4074367088607591</v>
+        <v>4.1379958246346558</v>
       </c>
       <c r="P55" s="9">
-        <v>13.48571428571428</v>
+        <v>12.05326086956522</v>
       </c>
       <c r="Q55" s="9">
-        <v>3.0201063098814478</v>
+        <v>2.5478485531839632</v>
       </c>
       <c r="R55" s="10">
-        <v>63.479941545278841</v>
+        <v>51.630292562935047</v>
       </c>
       <c r="S55" s="6">
-        <v>0.16340411265087171</v>
+        <v>0.14804156107450581</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B56" s="3">
         <v>46248</v>
       </c>
       <c r="C56" s="4">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D56" s="4">
-        <v>444</v>
+        <v>523</v>
       </c>
       <c r="E56" s="5">
-        <v>9.45945945945946E-2</v>
+        <v>-7.6481835564053538E-2</v>
       </c>
       <c r="F56" s="4">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="G56" s="6">
-        <v>0.19547325102880661</v>
+        <v>0.15734989648033129</v>
       </c>
       <c r="H56" s="7">
-        <v>0.22500000000000001</v>
+        <v>0.309</v>
       </c>
       <c r="I56" s="6">
-        <v>0.65500000000000003</v>
+        <v>0.745</v>
       </c>
       <c r="J56" s="4">
-        <v>186.26</v>
+        <v>212.69</v>
       </c>
       <c r="K56" s="6">
-        <v>0.26200000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="L56" s="2">
-        <v>-7.7400000000000091</v>
+        <v>-20.580000000000009</v>
       </c>
       <c r="M56" s="6">
-        <v>9.5000000000000001E-2</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="N56" s="6">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="O56" s="8">
-        <v>4.7144032921810686</v>
+        <v>11.138095238095239</v>
       </c>
       <c r="P56" s="9">
-        <v>12.287826086956519</v>
+        <v>16.652586206896551</v>
       </c>
       <c r="Q56" s="9">
-        <v>2.597418584980753</v>
+        <v>2.2961088753852819</v>
       </c>
       <c r="R56" s="10">
-        <v>53.95146569311715</v>
+        <v>48.511918754995527</v>
       </c>
       <c r="S56" s="6">
-        <v>0.1283023186386705</v>
+        <v>0.2011940298507463</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B57" s="3">
         <v>46248</v>
       </c>
       <c r="C57" s="4">
-        <v>643</v>
+        <v>484</v>
       </c>
       <c r="D57" s="4">
-        <v>588</v>
+        <v>420</v>
       </c>
       <c r="E57" s="5">
-        <v>9.3537414965986401E-2</v>
+        <v>0.15238095238095239</v>
       </c>
       <c r="F57" s="4">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="G57" s="6">
-        <v>0.25194401244167958</v>
+        <v>0.23347107438016529</v>
       </c>
       <c r="H57" s="7">
-        <v>0.224</v>
+        <v>0.21</v>
       </c>
       <c r="I57" s="6">
-        <v>0.71</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="J57" s="4">
-        <v>245.98</v>
+        <v>171.06</v>
       </c>
       <c r="K57" s="6">
-        <v>0.29799999999999999</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="L57" s="2">
-        <v>18.63999999999999</v>
+        <v>1.379999999999995</v>
       </c>
       <c r="M57" s="6">
-        <v>0.188</v>
+        <v>0.184</v>
       </c>
       <c r="N57" s="6">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="O57" s="8">
-        <v>8.2819595645412125</v>
+        <v>7.4138429752066122</v>
       </c>
       <c r="P57" s="9">
-        <v>14.22770491803279</v>
+        <v>12.69673202614379</v>
       </c>
       <c r="Q57" s="9">
-        <v>2.6309209637574731</v>
+        <v>2.8038179080731731</v>
       </c>
       <c r="R57" s="10">
-        <v>55.382551426945277</v>
+        <v>58.628551385478779</v>
       </c>
       <c r="S57" s="6">
-        <v>0.13378004851870909</v>
+        <v>0.13584790646547421</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B58" s="3">
         <v>46248</v>
       </c>
       <c r="C58" s="4">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="D58" s="4">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="E58" s="5">
-        <v>-6.8548387096774188E-2</v>
+        <v>9.45945945945946E-2</v>
       </c>
       <c r="F58" s="4">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G58" s="6">
-        <v>0.145021645021645</v>
+        <v>0.19547325102880661</v>
       </c>
       <c r="H58" s="7">
-        <v>0.223</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="I58" s="6">
-        <v>0.68300000000000005</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="J58" s="4">
-        <v>195.6</v>
+        <v>186.26</v>
       </c>
       <c r="K58" s="6">
-        <v>0.29099999999999998</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="L58" s="2">
-        <v>6.6800000000000068</v>
+        <v>-7.7400000000000091</v>
       </c>
       <c r="M58" s="6">
-        <v>6.9000000000000006E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="N58" s="6">
-        <v>7.0999999999999994E-2</v>
+        <v>0.12</v>
       </c>
       <c r="O58" s="8">
-        <v>3.2865800865800869</v>
+        <v>4.7144032921810686</v>
       </c>
       <c r="P58" s="9">
-        <v>12.07090909090909</v>
+        <v>12.287826086956519</v>
       </c>
       <c r="Q58" s="9">
-        <v>2.344890898142713</v>
+        <v>2.597418584980753</v>
       </c>
       <c r="R58" s="10">
-        <v>47.816973415132928</v>
+        <v>53.95146569311715</v>
       </c>
       <c r="S58" s="6">
-        <v>0.13657436116753979</v>
+        <v>0.1283023186386705</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="B59" s="3">
         <v>46248</v>
       </c>
       <c r="C59" s="4">
-        <v>331</v>
+        <v>488</v>
       </c>
       <c r="D59" s="4">
-        <v>347</v>
+        <v>443</v>
       </c>
       <c r="E59" s="5">
-        <v>-4.6109510086455328E-2</v>
+        <v>0.1015801354401806</v>
       </c>
       <c r="F59" s="4">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="G59" s="6">
-        <v>0.29607250755287012</v>
+        <v>0.24180327868852461</v>
       </c>
       <c r="H59" s="7">
-        <v>0.221</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="I59" s="6">
-        <v>0.72899999999999998</v>
+        <v>0.747</v>
       </c>
       <c r="J59" s="4">
-        <v>163.82</v>
+        <v>181.03</v>
       </c>
       <c r="K59" s="6">
-        <v>0.27200000000000002</v>
+        <v>0.311</v>
       </c>
       <c r="L59" s="2">
-        <v>-19.36000000000001</v>
+        <v>4.6599999999999966</v>
       </c>
       <c r="M59" s="6">
-        <v>0.245</v>
+        <v>0.191</v>
       </c>
       <c r="N59" s="6">
-        <v>0.24</v>
+        <v>0.153</v>
       </c>
       <c r="O59" s="8">
-        <v>10.02870090634441</v>
+        <v>7.8989754098360656</v>
       </c>
       <c r="P59" s="9">
-        <v>16.05103448275862</v>
+        <v>12.65674518201285</v>
       </c>
       <c r="Q59" s="9">
-        <v>2.0888004893419652</v>
+        <v>2.7413645847054671</v>
       </c>
       <c r="R59" s="10">
-        <v>41.899645952875112</v>
+        <v>57.846765729437109</v>
       </c>
       <c r="S59" s="6">
-        <v>6.367340955731457E-2</v>
+        <v>8.9945569136745604E-2</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3">
         <v>46248</v>
       </c>
       <c r="C60" s="4">
-        <v>335</v>
+        <v>498</v>
       </c>
       <c r="D60" s="4">
-        <v>323</v>
+        <v>471</v>
       </c>
       <c r="E60" s="5">
-        <v>3.7151702786377708E-2</v>
+        <v>5.7324840764331211E-2</v>
       </c>
       <c r="F60" s="4">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G60" s="6">
-        <v>0.33134328358208948</v>
+        <v>0.20883534136546181</v>
       </c>
       <c r="H60" s="7">
-        <v>0.217</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="I60" s="6">
-        <v>0.68899999999999995</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="J60" s="4">
-        <v>176.27</v>
+        <v>211.2</v>
       </c>
       <c r="K60" s="6">
-        <v>0.28299999999999997</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="L60" s="2">
-        <v>7.4000000000000057</v>
+        <v>13.44999999999999</v>
       </c>
       <c r="M60" s="6">
-        <v>0.28100000000000003</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="N60" s="6">
-        <v>0.28399999999999997</v>
+        <v>0.21</v>
       </c>
       <c r="O60" s="8">
-        <v>12.161194029850749</v>
+        <v>8.485140562248997</v>
       </c>
       <c r="P60" s="9">
-        <v>19.356393442622949</v>
+        <v>15.809484536082479</v>
       </c>
       <c r="Q60" s="9">
-        <v>1.906025175791233</v>
+        <v>2.3788252712890432</v>
       </c>
       <c r="R60" s="10">
-        <v>38.565836500822599</v>
+        <v>49.512310606060609</v>
       </c>
       <c r="S60" s="6">
-        <v>0.14636712409620781</v>
+        <v>0.15994549105862099</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B61" s="3">
         <v>46248</v>
       </c>
       <c r="C61" s="4">
-        <v>367</v>
+        <v>498</v>
       </c>
       <c r="D61" s="4">
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="E61" s="5">
-        <v>-0.11778846153846149</v>
+        <v>-7.9681274900398405E-3</v>
       </c>
       <c r="F61" s="4">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="G61" s="6">
-        <v>0.21798365122615801</v>
+        <v>0.29919678714859438</v>
       </c>
       <c r="H61" s="7">
-        <v>0.216</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="I61" s="6">
-        <v>0.749</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="J61" s="4">
-        <v>165</v>
+        <v>214.57</v>
       </c>
       <c r="K61" s="6">
-        <v>0.24399999999999999</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="L61" s="2">
-        <v>-7.6100000000000136</v>
+        <v>9.2399999999999807</v>
       </c>
       <c r="M61" s="6">
-        <v>0.193</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="N61" s="6">
-        <v>0.19800000000000001</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="O61" s="8">
-        <v>8.2119891008174388</v>
+        <v>7.5174698795180719</v>
       </c>
       <c r="P61" s="9">
-        <v>16.095845697329381</v>
+        <v>15.53970276008492</v>
       </c>
       <c r="Q61" s="9">
-        <v>2.265096144165911</v>
+        <v>2.3652817421598118</v>
       </c>
       <c r="R61" s="10">
-        <v>45.963636363636361</v>
+        <v>47.252644824532787</v>
       </c>
       <c r="S61" s="6">
-        <v>0.1101203226232976</v>
+        <v>0.2036217503472911</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B62" s="3">
         <v>46248</v>
       </c>
       <c r="C62" s="4">
-        <v>657</v>
+        <v>501</v>
       </c>
       <c r="D62" s="4">
-        <v>680</v>
+        <v>448</v>
       </c>
       <c r="E62" s="5">
-        <v>-3.3823529411764697E-2</v>
+        <v>0.1183035714285714</v>
       </c>
       <c r="F62" s="4">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="G62" s="6">
-        <v>0.21613394216133941</v>
+        <v>0.17764471057884229</v>
       </c>
       <c r="H62" s="7">
-        <v>0.216</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="I62" s="6">
-        <v>0.78600000000000003</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="J62" s="4">
-        <v>256.69</v>
+        <v>193.48</v>
       </c>
       <c r="K62" s="6">
-        <v>0.34100000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L62" s="2">
-        <v>8.2700000000000102</v>
+        <v>-0.30000000000001142</v>
       </c>
       <c r="M62" s="6">
-        <v>0.17799999999999999</v>
+        <v>0.248</v>
       </c>
       <c r="N62" s="6">
-        <v>0.28899999999999998</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="O62" s="8">
-        <v>7.0348554033485531</v>
+        <v>10.20578842315369</v>
       </c>
       <c r="P62" s="9">
-        <v>14.760389610389611</v>
+        <v>16.26032719836401</v>
       </c>
       <c r="Q62" s="9">
-        <v>2.6118257375184522</v>
+        <v>2.6048408519257431</v>
       </c>
       <c r="R62" s="10">
-        <v>53.363979897931358</v>
+        <v>54.822203845358693</v>
       </c>
       <c r="S62" s="6">
-        <v>0.15310147898667451</v>
+        <v>0.12293811998110531</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="B63" s="3">
         <v>46248</v>
       </c>
       <c r="C63" s="4">
-        <v>797</v>
+        <v>504</v>
       </c>
       <c r="D63" s="4">
-        <v>733</v>
+        <v>443</v>
       </c>
       <c r="E63" s="5">
-        <v>8.7312414733969987E-2</v>
+        <v>0.13769751693002261</v>
       </c>
       <c r="F63" s="4">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="G63" s="6">
-        <v>0.25972396486825589</v>
+        <v>0.30753968253968261</v>
       </c>
       <c r="H63" s="7">
-        <v>0.215</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="I63" s="6">
-        <v>0.73799999999999999</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="J63" s="4">
-        <v>322.11</v>
+        <v>235.45</v>
       </c>
       <c r="K63" s="6">
-        <v>0.30299999999999999</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="L63" s="2">
-        <v>17.949999999999989</v>
+        <v>35.269999999999982</v>
       </c>
       <c r="M63" s="6">
-        <v>0.26900000000000002</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="N63" s="6">
-        <v>0.39600000000000002</v>
+        <v>0.252</v>
       </c>
       <c r="O63" s="8">
-        <v>11.909284818067761</v>
+        <v>10.75238095238095</v>
       </c>
       <c r="P63" s="9">
-        <v>15.495108695652171</v>
+        <v>15.80194384449244</v>
       </c>
       <c r="Q63" s="9">
-        <v>2.577858850564732</v>
+        <v>2.1890089062899221</v>
       </c>
       <c r="R63" s="10">
-        <v>45.89115519543013</v>
+        <v>43.457209598640901</v>
       </c>
       <c r="S63" s="6">
-        <v>8.31710294317103E-2</v>
+        <v>0.10663470945020539</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3">
         <v>46248</v>
       </c>
       <c r="C64" s="4">
-        <v>400</v>
+        <v>508</v>
       </c>
       <c r="D64" s="4">
-        <v>394</v>
+        <v>570</v>
       </c>
       <c r="E64" s="5">
-        <v>1.522842639593909E-2</v>
+        <v>-0.10877192982456139</v>
       </c>
       <c r="F64" s="4">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="G64" s="6">
-        <v>0.27</v>
+        <v>0.25393700787401569</v>
       </c>
       <c r="H64" s="7">
-        <v>0.21299999999999999</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="I64" s="6">
-        <v>0.746</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="J64" s="4">
-        <v>169.09</v>
+        <v>190.48</v>
       </c>
       <c r="K64" s="6">
-        <v>0.26500000000000001</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="L64" s="2">
-        <v>-9.0799999999999841</v>
+        <v>-50.920000000000023</v>
       </c>
       <c r="M64" s="6">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="N64" s="6">
-        <v>0.17100000000000001</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="O64" s="8">
-        <v>6.2029999999999994</v>
+        <v>9.6255905511811033</v>
       </c>
       <c r="P64" s="9">
-        <v>13.972251308900519</v>
+        <v>14.87933884297521</v>
       </c>
       <c r="Q64" s="9">
-        <v>2.401135144066163</v>
+        <v>2.6997932546440722</v>
       </c>
       <c r="R64" s="10">
-        <v>47.980365485835947</v>
+        <v>53.023939521209577</v>
       </c>
       <c r="S64" s="6">
-        <v>0.20814306893995549</v>
+        <v>0.15787716159809179</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B65" s="3">
         <v>46248</v>
       </c>
       <c r="C65" s="4">
-        <v>427</v>
+        <v>515</v>
       </c>
       <c r="D65" s="4">
-        <v>401</v>
+        <v>467</v>
       </c>
       <c r="E65" s="5">
-        <v>6.4837905236907731E-2</v>
+        <v>0.1027837259100642</v>
       </c>
       <c r="F65" s="4">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G65" s="6">
-        <v>0.22248243559718969</v>
+        <v>0.2174757281553398</v>
       </c>
       <c r="H65" s="7">
-        <v>0.21299999999999999</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="I65" s="6">
-        <v>0.66300000000000003</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="J65" s="4">
-        <v>171.95</v>
+        <v>233.47</v>
       </c>
       <c r="K65" s="6">
-        <v>0.26400000000000001</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="L65" s="2">
-        <v>27.41</v>
+        <v>-23.900000000000009</v>
       </c>
       <c r="M65" s="6">
-        <v>0.10100000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="N65" s="6">
-        <v>0.24099999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="O65" s="8">
-        <v>4.9046838407494153</v>
+        <v>5.4040776699029127</v>
       </c>
       <c r="P65" s="9">
-        <v>12.42493827160494</v>
+        <v>15.237909836065571</v>
       </c>
       <c r="Q65" s="9">
-        <v>2.509309278859432</v>
+        <v>2.212808375265805</v>
       </c>
       <c r="R65" s="10">
-        <v>49.717941261994767</v>
+        <v>45.397695635413541</v>
       </c>
       <c r="S65" s="6">
-        <v>0.1046787807737397</v>
+        <v>0.14903858854608931</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B66" s="3">
-        <v>46248</v>
-      </c>
-      <c r="C66" s="4">
-        <v>465</v>
-      </c>
-      <c r="D66" s="4">
-        <v>450</v>
-      </c>
-      <c r="E66" s="5">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="F66" s="4">
-        <v>96</v>
-      </c>
-      <c r="G66" s="6">
-        <v>0.20645161290322581</v>
-      </c>
-      <c r="H66" s="7">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="I66" s="6">
-        <v>0.64100000000000001</v>
-      </c>
-      <c r="J66" s="4">
-        <v>196.83</v>
-      </c>
-      <c r="K66" s="6">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="L66" s="2">
-        <v>15.03</v>
-      </c>
-      <c r="M66" s="6">
-        <v>0.247</v>
-      </c>
-      <c r="N66" s="6">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="O66" s="8">
-        <v>10.0705376344086</v>
-      </c>
-      <c r="P66" s="9">
-        <v>16.278571428571428</v>
-      </c>
-      <c r="Q66" s="9">
-        <v>2.4286590816083269</v>
-      </c>
-      <c r="R66" s="10">
-        <v>48.51394604481024</v>
-      </c>
-      <c r="S66" s="6">
-        <v>0.11919049115090589</v>
+      <c r="A66" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="12">
+        <v>46248</v>
+      </c>
+      <c r="C66" s="13">
+        <v>518</v>
+      </c>
+      <c r="D66" s="13">
+        <v>396</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0.30808080808080812</v>
+      </c>
+      <c r="F66" s="13">
+        <v>105</v>
+      </c>
+      <c r="G66" s="15">
+        <v>0.20270270270270269</v>
+      </c>
+      <c r="H66" s="16">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="I66" s="15">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="J66" s="13">
+        <v>184.78</v>
+      </c>
+      <c r="K66" s="15">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="L66" s="11">
+        <v>25.37</v>
+      </c>
+      <c r="M66" s="15">
+        <v>0.125</v>
+      </c>
+      <c r="N66" s="15">
+        <v>0.122</v>
+      </c>
+      <c r="O66" s="17">
+        <v>4.807722007722008</v>
+      </c>
+      <c r="P66" s="18">
+        <v>15.22464646464646</v>
+      </c>
+      <c r="Q66" s="18">
+        <v>2.853295191570838</v>
+      </c>
+      <c r="R66" s="19">
+        <v>55.850200238121012</v>
+      </c>
+      <c r="S66" s="15">
+        <v>0.1107237354085603</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B67" s="3">
         <v>46248</v>
       </c>
       <c r="C67" s="4">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="D67" s="4">
-        <v>448</v>
+        <v>496</v>
       </c>
       <c r="E67" s="5">
-        <v>0.1183035714285714</v>
+        <v>4.8387096774193547E-2</v>
       </c>
       <c r="F67" s="4">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="G67" s="6">
-        <v>0.17764471057884229</v>
+        <v>0.24038461538461539</v>
       </c>
       <c r="H67" s="7">
-        <v>0.21099999999999999</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="I67" s="6">
-        <v>0.82199999999999995</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="J67" s="4">
-        <v>193.48</v>
+        <v>195.92</v>
       </c>
       <c r="K67" s="6">
-        <v>0.28999999999999998</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="L67" s="2">
-        <v>-0.30000000000001142</v>
+        <v>3.4799999999999902</v>
       </c>
       <c r="M67" s="6">
-        <v>0.248</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="N67" s="6">
-        <v>0.16700000000000001</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="O67" s="8">
-        <v>10.20578842315369</v>
+        <v>6.18</v>
       </c>
       <c r="P67" s="9">
-        <v>16.26032719836401</v>
+        <v>14.865243902439021</v>
       </c>
       <c r="Q67" s="9">
-        <v>2.6048408519257431</v>
+        <v>2.7136004545556589</v>
       </c>
       <c r="R67" s="10">
-        <v>54.822203845358693</v>
+        <v>53.756635361371991</v>
       </c>
       <c r="S67" s="6">
-        <v>0.12293811998110531</v>
+        <v>0.1327328070008561</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B68" s="3">
         <v>46248</v>
       </c>
       <c r="C68" s="4">
-        <v>484</v>
+        <v>520</v>
       </c>
       <c r="D68" s="4">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="E68" s="5">
-        <v>0.15238095238095239</v>
+        <v>9.4736842105263161E-2</v>
       </c>
       <c r="F68" s="4">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G68" s="6">
-        <v>0.23347107438016529</v>
+        <v>0.19807692307692309</v>
       </c>
       <c r="H68" s="7">
-        <v>0.21</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="I68" s="6">
-        <v>0.71199999999999997</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="J68" s="4">
-        <v>171.06</v>
+        <v>199.61</v>
       </c>
       <c r="K68" s="6">
-        <v>0.25700000000000001</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="L68" s="2">
-        <v>1.379999999999995</v>
+        <v>17.710000000000012</v>
       </c>
       <c r="M68" s="6">
-        <v>0.184</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="N68" s="6">
-        <v>0.25</v>
+        <v>0.107</v>
       </c>
       <c r="O68" s="8">
-        <v>7.4138429752066122</v>
+        <v>6.2301923076923069</v>
       </c>
       <c r="P68" s="9">
-        <v>12.69673202614379</v>
+        <v>15.781000000000001</v>
       </c>
       <c r="Q68" s="9">
-        <v>2.8038179080731731</v>
+        <v>2.627345009980556</v>
       </c>
       <c r="R68" s="10">
-        <v>58.628551385478779</v>
+        <v>53.078503081007959</v>
       </c>
       <c r="S68" s="6">
-        <v>0.13584790646547421</v>
+        <v>0.16363190184049081</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
@@ -4907,1359 +4899,1359 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B70" s="3">
         <v>46248</v>
       </c>
       <c r="C70" s="4">
-        <v>428</v>
+        <v>528</v>
       </c>
       <c r="D70" s="4">
-        <v>386</v>
+        <v>558</v>
       </c>
       <c r="E70" s="5">
-        <v>0.1088082901554404</v>
+        <v>-5.3763440860215048E-2</v>
       </c>
       <c r="F70" s="4">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="G70" s="6">
-        <v>0.27570093457943923</v>
+        <v>0.19886363636363641</v>
       </c>
       <c r="H70" s="7">
-        <v>0.20699999999999999</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="I70" s="6">
-        <v>0.70299999999999996</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="J70" s="4">
-        <v>189.23</v>
+        <v>182.64</v>
       </c>
       <c r="K70" s="6">
-        <v>0.27</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="L70" s="2">
-        <v>22.349999999999991</v>
+        <v>-16.44000000000003</v>
       </c>
       <c r="M70" s="6">
-        <v>0.17299999999999999</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="N70" s="6">
-        <v>0.19</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="O70" s="8">
-        <v>6.8899532710280376</v>
+        <v>10.14488636363636</v>
       </c>
       <c r="P70" s="9">
-        <v>15.1953431372549</v>
+        <v>14.38198757763975</v>
       </c>
       <c r="Q70" s="9">
-        <v>2.3039136310839532</v>
+        <v>2.993477918626374</v>
       </c>
       <c r="R70" s="10">
-        <v>46.218887068646623</v>
+        <v>60.731493648707847</v>
       </c>
       <c r="S70" s="6">
-        <v>0.1470706608735422</v>
+        <v>0.12324918566775241</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B71" s="3">
         <v>46248</v>
       </c>
       <c r="C71" s="4">
-        <v>360</v>
+        <v>544</v>
       </c>
       <c r="D71" s="4">
-        <v>325</v>
+        <v>584</v>
       </c>
       <c r="E71" s="5">
-        <v>0.1076923076923077</v>
+        <v>-6.8493150684931503E-2</v>
       </c>
       <c r="F71" s="4">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="G71" s="6">
-        <v>0.21111111111111111</v>
+        <v>0.2095588235294118</v>
       </c>
       <c r="H71" s="7">
-        <v>0.20399999999999999</v>
+        <v>0.254</v>
       </c>
       <c r="I71" s="6">
-        <v>0.73099999999999998</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="J71" s="4">
-        <v>168.79</v>
+        <v>235.46</v>
       </c>
       <c r="K71" s="6">
-        <v>0.313</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="L71" s="2">
-        <v>-5.2000000000000171</v>
+        <v>-9.3899999999999864</v>
       </c>
       <c r="M71" s="6">
-        <v>0.22500000000000001</v>
+        <v>0.182</v>
       </c>
       <c r="N71" s="6">
-        <v>0.313</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="O71" s="8">
-        <v>9.2761111111111116</v>
+        <v>7.1389705882352938</v>
       </c>
       <c r="P71" s="9">
-        <v>15.927352941176469</v>
+        <v>15.324427480916031</v>
       </c>
       <c r="Q71" s="9">
-        <v>2.153878733866708</v>
+        <v>2.3389575204870572</v>
       </c>
       <c r="R71" s="10">
-        <v>43.385271639315128</v>
+        <v>49.605028454939273</v>
       </c>
       <c r="S71" s="6">
-        <v>0.1115502602026842</v>
+        <v>0.15082388316151199</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B72" s="3">
         <v>46248</v>
       </c>
       <c r="C72" s="4">
-        <v>508</v>
+        <v>550</v>
       </c>
       <c r="D72" s="4">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="E72" s="5">
-        <v>-0.10877192982456139</v>
+        <v>0.14583333333333329</v>
       </c>
       <c r="F72" s="4">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="G72" s="6">
-        <v>0.25393700787401569</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="H72" s="7">
-        <v>0.20300000000000001</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="I72" s="6">
-        <v>0.71399999999999997</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="J72" s="4">
-        <v>190.48</v>
+        <v>191.88</v>
       </c>
       <c r="K72" s="6">
-        <v>0.26700000000000002</v>
+        <v>0.374</v>
       </c>
       <c r="L72" s="2">
-        <v>-50.920000000000023</v>
+        <v>9.0600000000000023</v>
       </c>
       <c r="M72" s="6">
-        <v>0.24</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="N72" s="6">
-        <v>0.28499999999999998</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="O72" s="8">
-        <v>9.6255905511811033</v>
+        <v>5.8134545454545457</v>
       </c>
       <c r="P72" s="9">
-        <v>14.87933884297521</v>
+        <v>14.90888468809074</v>
       </c>
       <c r="Q72" s="9">
-        <v>2.6997932546440722</v>
+        <v>2.8984332839953759</v>
       </c>
       <c r="R72" s="10">
-        <v>53.023939521209577</v>
+        <v>61.340421096518661</v>
       </c>
       <c r="S72" s="6">
-        <v>0.15787716159809179</v>
+        <v>0.1190637213254036</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B73" s="3">
         <v>46248</v>
       </c>
       <c r="C73" s="4">
-        <v>479</v>
+        <v>551</v>
       </c>
       <c r="D73" s="4">
-        <v>618</v>
+        <v>516</v>
       </c>
       <c r="E73" s="5">
-        <v>-0.22491909385113271</v>
+        <v>6.7829457364341081E-2</v>
       </c>
       <c r="F73" s="4">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="G73" s="6">
-        <v>0.23799582463465549</v>
+        <v>0.29219600725952821</v>
       </c>
       <c r="H73" s="7">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I73" s="6">
+        <v>0.752</v>
+      </c>
+      <c r="J73" s="4">
+        <v>219.51</v>
+      </c>
+      <c r="K73" s="6">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="L73" s="2">
+        <v>22.259999999999991</v>
+      </c>
+      <c r="M73" s="6">
         <v>0.2</v>
       </c>
-      <c r="I73" s="6">
-        <v>0.77700000000000002</v>
-      </c>
-      <c r="J73" s="4">
-        <v>191.07</v>
-      </c>
-      <c r="K73" s="6">
-        <v>0.311</v>
-      </c>
-      <c r="L73" s="2">
-        <v>-29.28</v>
-      </c>
-      <c r="M73" s="6">
-        <v>7.2999999999999995E-2</v>
-      </c>
       <c r="N73" s="6">
-        <v>8.6999999999999994E-2</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="O73" s="8">
-        <v>4.1379958246346558</v>
+        <v>8.2709618874773145</v>
       </c>
       <c r="P73" s="9">
-        <v>12.05326086956522</v>
+        <v>15.91257035647279</v>
       </c>
       <c r="Q73" s="9">
-        <v>2.5478485531839632</v>
+        <v>2.5414995211359841</v>
       </c>
       <c r="R73" s="10">
-        <v>51.630292562935047</v>
+        <v>51.423625347364577</v>
       </c>
       <c r="S73" s="6">
-        <v>0.14804156107450581</v>
+        <v>0.1981728636081285</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="B74" s="3">
         <v>46248</v>
       </c>
       <c r="C74" s="4">
-        <v>397</v>
+        <v>560</v>
       </c>
       <c r="D74" s="4">
-        <v>414</v>
+        <v>461</v>
       </c>
       <c r="E74" s="5">
-        <v>-4.1062801932367152E-2</v>
+        <v>0.2147505422993492</v>
       </c>
       <c r="F74" s="4">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="G74" s="6">
-        <v>0.22166246851385391</v>
+        <v>0.26964285714285707</v>
       </c>
       <c r="H74" s="7">
-        <v>0.2</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="I74" s="6">
-        <v>0.73199999999999998</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="J74" s="4">
-        <v>159.78</v>
+        <v>199.2</v>
       </c>
       <c r="K74" s="6">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="L74" s="2">
-        <v>-7.9199999999999866</v>
+        <v>9.8699999999999761</v>
       </c>
       <c r="M74" s="6">
-        <v>0.214</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="N74" s="6">
-        <v>0.33300000000000002</v>
+        <v>0.309</v>
       </c>
       <c r="O74" s="8">
-        <v>8.5012594458438286</v>
+        <v>10.73964285714286</v>
       </c>
       <c r="P74" s="9">
-        <v>15.005804749340371</v>
+        <v>14.61047794117647</v>
       </c>
       <c r="Q74" s="9">
-        <v>2.5309686194965959</v>
+        <v>2.855332654866479</v>
       </c>
       <c r="R74" s="10">
-        <v>53.648767054700222</v>
+        <v>60.712851405622487</v>
       </c>
       <c r="S74" s="6">
-        <v>0.17672240411599621</v>
+        <v>0.1483851496609889</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B75" s="3">
         <v>46248</v>
       </c>
       <c r="C75" s="4">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="D75" s="4">
-        <v>520</v>
+        <v>628</v>
       </c>
       <c r="E75" s="5">
-        <v>0.16346153846153849</v>
+        <v>-8.9171974522292988E-2</v>
       </c>
       <c r="F75" s="4">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="G75" s="6">
-        <v>0.28925619834710742</v>
+        <v>0.17832167832167831</v>
       </c>
       <c r="H75" s="7">
-        <v>0.19800000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="I75" s="6">
-        <v>0.71499999999999997</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="J75" s="4">
-        <v>258.69</v>
+        <v>205.61</v>
       </c>
       <c r="K75" s="6">
-        <v>0.28899999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="L75" s="2">
-        <v>-6.3299999999999841</v>
+        <v>-53.610000000000007</v>
       </c>
       <c r="M75" s="6">
-        <v>0.20699999999999999</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="N75" s="6">
-        <v>9.2999999999999999E-2</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="O75" s="8">
-        <v>9.5894214876033068</v>
+        <v>8.5608391608391603</v>
       </c>
       <c r="P75" s="9">
-        <v>17.101730103806229</v>
+        <v>15.185766423357659</v>
       </c>
       <c r="Q75" s="9">
-        <v>2.3611565887182628</v>
+        <v>2.8291561332288868</v>
       </c>
       <c r="R75" s="10">
-        <v>46.901697011867483</v>
+        <v>60.035990467389723</v>
       </c>
       <c r="S75" s="6">
-        <v>0.13468861136382429</v>
+        <v>0.16363577446532729</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B76" s="3">
         <v>46248</v>
       </c>
       <c r="C76" s="4">
-        <v>727</v>
+        <v>582</v>
       </c>
       <c r="D76" s="4">
-        <v>706</v>
+        <v>460</v>
       </c>
       <c r="E76" s="5">
-        <v>2.9745042492917852E-2</v>
+        <v>0.26521739130434779</v>
       </c>
       <c r="F76" s="4">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="G76" s="6">
-        <v>0.22420907840440171</v>
+        <v>0.23367697594501721</v>
       </c>
       <c r="H76" s="7">
-        <v>0.19800000000000001</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="I76" s="6">
-        <v>0.65600000000000003</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="J76" s="4">
-        <v>350.3</v>
+        <v>244.5</v>
       </c>
       <c r="K76" s="6">
-        <v>0.30599999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="L76" s="2">
-        <v>-1.3000000000000109</v>
+        <v>42.81</v>
       </c>
       <c r="M76" s="6">
-        <v>0.45400000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="N76" s="6">
-        <v>0.54100000000000004</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="O76" s="8">
-        <v>20.202888583218709</v>
+        <v>7.0587628865979379</v>
       </c>
       <c r="P76" s="9">
-        <v>19.30117994100295</v>
+        <v>15.0705565529623</v>
       </c>
       <c r="Q76" s="9">
-        <v>2.1617372195798019</v>
+        <v>2.3889493969972819</v>
       </c>
       <c r="R76" s="10">
-        <v>36.01484441906937</v>
+        <v>41.93047034764826</v>
       </c>
       <c r="S76" s="6">
-        <v>4.9967478385024203E-2</v>
+        <v>7.3770155379654062E-2</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B77" s="3">
         <v>46248</v>
       </c>
       <c r="C77" s="4">
-        <v>572</v>
+        <v>605</v>
       </c>
       <c r="D77" s="4">
-        <v>628</v>
+        <v>520</v>
       </c>
       <c r="E77" s="5">
-        <v>-8.9171974522292988E-2</v>
+        <v>0.16346153846153849</v>
       </c>
       <c r="F77" s="4">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="G77" s="6">
-        <v>0.17832167832167831</v>
+        <v>0.28925619834710742</v>
       </c>
       <c r="H77" s="7">
-        <v>0.19</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I77" s="6">
-        <v>0.78800000000000003</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="J77" s="4">
-        <v>205.61</v>
+        <v>258.69</v>
       </c>
       <c r="K77" s="6">
-        <v>0.25</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="L77" s="2">
-        <v>-53.610000000000007</v>
+        <v>-6.3299999999999841</v>
       </c>
       <c r="M77" s="6">
-        <v>0.19400000000000001</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="N77" s="6">
-        <v>0.25900000000000001</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="O77" s="8">
-        <v>8.5608391608391603</v>
+        <v>9.5894214876033068</v>
       </c>
       <c r="P77" s="9">
-        <v>15.185766423357659</v>
+        <v>17.101730103806229</v>
       </c>
       <c r="Q77" s="9">
-        <v>2.8291561332288868</v>
+        <v>2.3611565887182628</v>
       </c>
       <c r="R77" s="10">
-        <v>60.035990467389723</v>
+        <v>46.901697011867483</v>
       </c>
       <c r="S77" s="6">
-        <v>0.16363577446532729</v>
+        <v>0.13468861136382429</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="B78" s="3">
         <v>46248</v>
       </c>
       <c r="C78" s="4">
-        <v>348</v>
+        <v>631</v>
       </c>
       <c r="D78" s="4">
-        <v>340</v>
+        <v>593</v>
       </c>
       <c r="E78" s="5">
-        <v>2.3529411764705879E-2</v>
+        <v>6.4080944350758853E-2</v>
       </c>
       <c r="F78" s="4">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="G78" s="6">
-        <v>0.23563218390804599</v>
+        <v>0.21236133122028519</v>
       </c>
       <c r="H78" s="7">
-        <v>0.185</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="I78" s="6">
-        <v>0.61599999999999999</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="J78" s="4">
-        <v>156.47999999999999</v>
+        <v>230.51</v>
       </c>
       <c r="K78" s="6">
-        <v>0.29699999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="L78" s="2">
-        <v>-42.52000000000001</v>
+        <v>10.259999999999989</v>
       </c>
       <c r="M78" s="6">
-        <v>0.161</v>
+        <v>0.192</v>
       </c>
       <c r="N78" s="6">
-        <v>0.182</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="O78" s="8">
-        <v>7.126724137931034</v>
+        <v>8.6516640253565757</v>
       </c>
       <c r="P78" s="9">
-        <v>15.066765578635019</v>
+        <v>12.87091836734694</v>
       </c>
       <c r="Q78" s="9">
-        <v>2.241837629687998</v>
+        <v>2.8485154653378948</v>
       </c>
       <c r="R78" s="10">
-        <v>42.497443762781188</v>
+        <v>53.815452691857189</v>
       </c>
       <c r="S78" s="6">
-        <v>0.20714586466165411</v>
+        <v>8.802745256358499E-2</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B79" s="3">
         <v>46248</v>
       </c>
       <c r="C79" s="4">
-        <v>520</v>
+        <v>632</v>
       </c>
       <c r="D79" s="4">
-        <v>496</v>
+        <v>617</v>
       </c>
       <c r="E79" s="5">
-        <v>4.8387096774193547E-2</v>
+        <v>2.4311183144246351E-2</v>
       </c>
       <c r="F79" s="4">
         <v>125</v>
       </c>
       <c r="G79" s="6">
-        <v>0.24038461538461539</v>
+        <v>0.19778481012658231</v>
       </c>
       <c r="H79" s="7">
-        <v>0.17499999999999999</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="I79" s="6">
-        <v>0.76100000000000001</v>
+        <v>0.72899999999999998</v>
       </c>
       <c r="J79" s="4">
-        <v>195.92</v>
+        <v>212.13</v>
       </c>
       <c r="K79" s="6">
-        <v>0.25700000000000001</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="L79" s="2">
-        <v>3.4799999999999902</v>
+        <v>-29.63</v>
       </c>
       <c r="M79" s="6">
-        <v>0.14799999999999999</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="N79" s="6">
-        <v>0.14399999999999999</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="O79" s="8">
-        <v>6.18</v>
+        <v>6.4074367088607591</v>
       </c>
       <c r="P79" s="9">
-        <v>14.865243902439021</v>
+        <v>13.48571428571428</v>
       </c>
       <c r="Q79" s="9">
-        <v>2.7136004545556589</v>
+        <v>3.0201063098814478</v>
       </c>
       <c r="R79" s="10">
-        <v>53.756635361371991</v>
+        <v>63.479941545278841</v>
       </c>
       <c r="S79" s="6">
-        <v>0.1327328070008561</v>
+        <v>0.16340411265087171</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B80" s="3">
         <v>46248</v>
       </c>
       <c r="C80" s="4">
-        <v>498</v>
+        <v>641</v>
       </c>
       <c r="D80" s="4">
-        <v>471</v>
+        <v>571</v>
       </c>
       <c r="E80" s="5">
-        <v>5.7324840764331211E-2</v>
+        <v>0.1225919439579685</v>
       </c>
       <c r="F80" s="4">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="G80" s="6">
-        <v>0.20883534136546181</v>
+        <v>0.26677067082683309</v>
       </c>
       <c r="H80" s="7">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="I80" s="6">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="J80" s="4">
+        <v>260.98</v>
+      </c>
+      <c r="K80" s="6">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="L80" s="2">
+        <v>18.900000000000009</v>
+      </c>
+      <c r="M80" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="I80" s="6">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="J80" s="4">
-        <v>211.2</v>
-      </c>
-      <c r="K80" s="6">
-        <v>0.26900000000000002</v>
-      </c>
-      <c r="L80" s="2">
-        <v>13.44999999999999</v>
-      </c>
-      <c r="M80" s="6">
-        <v>0.20100000000000001</v>
-      </c>
       <c r="N80" s="6">
-        <v>0.21</v>
+        <v>0.154</v>
       </c>
       <c r="O80" s="8">
-        <v>8.485140562248997</v>
+        <v>7.6770670826833074</v>
       </c>
       <c r="P80" s="9">
-        <v>15.809484536082479</v>
+        <v>14.986423841059599</v>
       </c>
       <c r="Q80" s="9">
-        <v>2.3788252712890432</v>
+        <v>2.5249317945142371</v>
       </c>
       <c r="R80" s="10">
-        <v>49.512310606060609</v>
+        <v>50.586251820062827</v>
       </c>
       <c r="S80" s="6">
-        <v>0.15994549105862099</v>
+        <v>0.13505440986226311</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B81" s="3">
         <v>46248</v>
       </c>
       <c r="C81" s="4">
-        <v>498</v>
+        <v>643</v>
       </c>
       <c r="D81" s="4">
-        <v>502</v>
+        <v>588</v>
       </c>
       <c r="E81" s="5">
-        <v>-7.9681274900398405E-3</v>
+        <v>9.3537414965986401E-2</v>
       </c>
       <c r="F81" s="4">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G81" s="6">
-        <v>0.29919678714859438</v>
+        <v>0.25194401244167958</v>
       </c>
       <c r="H81" s="7">
-        <v>0.17299999999999999</v>
+        <v>0.224</v>
       </c>
       <c r="I81" s="6">
-        <v>0.69799999999999995</v>
+        <v>0.71</v>
       </c>
       <c r="J81" s="4">
-        <v>214.57</v>
+        <v>245.98</v>
       </c>
       <c r="K81" s="6">
-        <v>0.29099999999999998</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="L81" s="2">
-        <v>9.2399999999999807</v>
+        <v>18.63999999999999</v>
       </c>
       <c r="M81" s="6">
-        <v>0.16300000000000001</v>
+        <v>0.188</v>
       </c>
       <c r="N81" s="6">
-        <v>0.16700000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="O81" s="8">
-        <v>7.5174698795180719</v>
+        <v>8.2819595645412125</v>
       </c>
       <c r="P81" s="9">
-        <v>15.53970276008492</v>
+        <v>14.22770491803279</v>
       </c>
       <c r="Q81" s="9">
-        <v>2.3652817421598118</v>
+        <v>2.6309209637574731</v>
       </c>
       <c r="R81" s="10">
-        <v>47.252644824532787</v>
+        <v>55.382551426945277</v>
       </c>
       <c r="S81" s="6">
-        <v>0.2036217503472911</v>
+        <v>0.13378004851870909</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B82" s="3">
         <v>46248</v>
       </c>
       <c r="C82" s="4">
-        <v>411</v>
+        <v>647</v>
       </c>
       <c r="D82" s="4">
-        <v>391</v>
+        <v>537</v>
       </c>
       <c r="E82" s="5">
-        <v>5.1150895140664961E-2</v>
+        <v>0.2048417132216015</v>
       </c>
       <c r="F82" s="4">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="G82" s="6">
-        <v>0.20924574209245739</v>
+        <v>0.2395672333848532</v>
       </c>
       <c r="H82" s="7">
-        <v>0.17199999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="I82" s="6">
-        <v>0.77900000000000003</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="J82" s="4">
-        <v>163.25</v>
+        <v>248.49</v>
       </c>
       <c r="K82" s="6">
-        <v>0.29099999999999998</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="L82" s="2">
-        <v>9.0000000000003411E-2</v>
+        <v>60.69</v>
       </c>
       <c r="M82" s="6">
-        <v>0.13900000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="N82" s="6">
-        <v>0.2</v>
+        <v>0.316</v>
       </c>
       <c r="O82" s="8">
-        <v>5.7153284671532836</v>
+        <v>13.94899536321484</v>
       </c>
       <c r="P82" s="9">
-        <v>13.94230769230769</v>
+        <v>16.701482701812189</v>
       </c>
       <c r="Q82" s="9">
-        <v>2.5496718796351558</v>
+        <v>2.672606342323355</v>
       </c>
       <c r="R82" s="10">
-        <v>54.603369065849932</v>
+        <v>53.205360376675117</v>
       </c>
       <c r="S82" s="6">
-        <v>0.15757606490872211</v>
+        <v>0.14885714285714291</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B83" s="3">
         <v>46248</v>
       </c>
       <c r="C83" s="4">
-        <v>428</v>
+        <v>657</v>
       </c>
       <c r="D83" s="4">
-        <v>444</v>
+        <v>680</v>
       </c>
       <c r="E83" s="5">
-        <v>-3.6036036036036043E-2</v>
+        <v>-3.3823529411764697E-2</v>
       </c>
       <c r="F83" s="4">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G83" s="6">
-        <v>0.28271028037383178</v>
+        <v>0.21613394216133941</v>
       </c>
       <c r="H83" s="7">
-        <v>0.17100000000000001</v>
+        <v>0.216</v>
       </c>
       <c r="I83" s="6">
-        <v>0.71399999999999997</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="J83" s="4">
-        <v>171.99</v>
+        <v>256.69</v>
       </c>
       <c r="K83" s="6">
-        <v>0.29399999999999998</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="L83" s="2">
-        <v>-37.699999999999989</v>
+        <v>8.2700000000000102</v>
       </c>
       <c r="M83" s="6">
-        <v>0.20599999999999999</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="N83" s="6">
-        <v>0.25700000000000001</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="O83" s="8">
-        <v>8.6852803738317768</v>
+        <v>7.0348554033485531</v>
       </c>
       <c r="P83" s="9">
-        <v>15.47164179104478</v>
+        <v>14.760389610389611</v>
       </c>
       <c r="Q83" s="9">
-        <v>2.525083238363389</v>
+        <v>2.6118257375184522</v>
       </c>
       <c r="R83" s="10">
-        <v>51.247165532879819</v>
+        <v>53.363979897931358</v>
       </c>
       <c r="S83" s="6">
-        <v>0.1469559791241207</v>
+        <v>0.15310147898667451</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="B84" s="3">
         <v>46248</v>
       </c>
       <c r="C84" s="4">
-        <v>378</v>
+        <v>669</v>
       </c>
       <c r="D84" s="4">
-        <v>389</v>
+        <v>604</v>
       </c>
       <c r="E84" s="5">
-        <v>-2.8277634961439591E-2</v>
+        <v>0.10761589403973509</v>
       </c>
       <c r="F84" s="4">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G84" s="6">
-        <v>0.23544973544973541</v>
+        <v>0.1599402092675635</v>
       </c>
       <c r="H84" s="7">
-        <v>0.17100000000000001</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="I84" s="6">
-        <v>0.71899999999999997</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="J84" s="4">
-        <v>160.33000000000001</v>
+        <v>244.58</v>
       </c>
       <c r="K84" s="6">
-        <v>0.26</v>
+        <v>0.316</v>
       </c>
       <c r="L84" s="2">
-        <v>-27.859999999999989</v>
+        <v>38.230000000000018</v>
       </c>
       <c r="M84" s="6">
-        <v>0.20100000000000001</v>
+        <v>9.4E-2</v>
       </c>
       <c r="N84" s="6">
-        <v>0.22700000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O84" s="8">
-        <v>8.299206349206349</v>
+        <v>5.1059790732436472</v>
       </c>
       <c r="P84" s="9">
-        <v>13.573579545454541</v>
+        <v>13.595911949685529</v>
       </c>
       <c r="Q84" s="9">
-        <v>2.3591878110345319</v>
+        <v>2.7572901950398681</v>
       </c>
       <c r="R84" s="10">
-        <v>49.722447452129977</v>
+        <v>55.556464142611823</v>
       </c>
       <c r="S84" s="6">
-        <v>0.15795283492222781</v>
+        <v>0.11640344421548431</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="B85" s="3">
         <v>46248</v>
       </c>
       <c r="C85" s="4">
-        <v>243</v>
+        <v>676</v>
       </c>
       <c r="D85" s="4">
-        <v>305</v>
+        <v>678</v>
       </c>
       <c r="E85" s="5">
-        <v>-0.20327868852459019</v>
+        <v>-2.9498525073746308E-3</v>
       </c>
       <c r="F85" s="4">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="G85" s="6">
-        <v>0.2139917695473251</v>
+        <v>0.16715976331360949</v>
       </c>
       <c r="H85" s="7">
-        <v>0.17100000000000001</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="I85" s="6">
-        <v>0.747</v>
+        <v>0.81599999999999995</v>
       </c>
       <c r="J85" s="4">
-        <v>145.72</v>
+        <v>229.76</v>
       </c>
       <c r="K85" s="6">
-        <v>0.315</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="L85" s="2">
-        <v>-19.650000000000009</v>
+        <v>-24.580000000000009</v>
       </c>
       <c r="M85" s="6">
-        <v>0.16500000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="N85" s="6">
-        <v>0.156</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="O85" s="8">
-        <v>6.632921810699588</v>
+        <v>6.2862426035502956</v>
       </c>
       <c r="P85" s="9">
-        <v>16.561802575107301</v>
+        <v>14.371517996870111</v>
       </c>
       <c r="Q85" s="9">
-        <v>1.697013499790986</v>
+        <v>3.011073942816751</v>
       </c>
       <c r="R85" s="10">
-        <v>34.332967334614331</v>
+        <v>61.738335654596099</v>
       </c>
       <c r="S85" s="6">
-        <v>0.15003397961223269</v>
+        <v>0.12478941798941801</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="B86" s="3">
         <v>46248</v>
       </c>
       <c r="C86" s="4">
-        <v>391</v>
+        <v>694</v>
       </c>
       <c r="D86" s="4">
-        <v>272</v>
+        <v>616</v>
       </c>
       <c r="E86" s="5">
-        <v>0.4375</v>
+        <v>0.12662337662337661</v>
       </c>
       <c r="F86" s="4">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="G86" s="6">
-        <v>0.32992327365728902</v>
+        <v>0.20893371757925069</v>
       </c>
       <c r="H86" s="7">
-        <v>0.16700000000000001</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="I86" s="6">
-        <v>0.67500000000000004</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="J86" s="4">
-        <v>168.01</v>
+        <v>272.42</v>
       </c>
       <c r="K86" s="6">
-        <v>0.23899999999999999</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="L86" s="2">
-        <v>20.829999999999981</v>
+        <v>-5.2899999999999636</v>
       </c>
       <c r="M86" s="6">
-        <v>0.161</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="N86" s="6">
-        <v>0.28199999999999997</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="O86" s="8">
-        <v>7.0583120204603587</v>
+        <v>5.6350144092219017</v>
       </c>
       <c r="P86" s="9">
-        <v>15.44393530997305</v>
+        <v>13.295833333333331</v>
       </c>
       <c r="Q86" s="9">
-        <v>2.3448410433080782</v>
+        <v>2.5559461431156438</v>
       </c>
       <c r="R86" s="10">
-        <v>45.693708707815013</v>
+        <v>53.652448425225749</v>
       </c>
       <c r="S86" s="6">
-        <v>0.1199960825280752</v>
+        <v>0.14011922707962179</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="B87" s="3">
         <v>46248</v>
       </c>
       <c r="C87" s="4">
-        <v>384</v>
+        <v>727</v>
       </c>
       <c r="D87" s="4">
-        <v>326</v>
+        <v>706</v>
       </c>
       <c r="E87" s="5">
-        <v>0.17791411042944791</v>
+        <v>2.9745042492917852E-2</v>
       </c>
       <c r="F87" s="4">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="G87" s="6">
-        <v>0.30208333333333331</v>
+        <v>0.22420907840440171</v>
       </c>
       <c r="H87" s="7">
-        <v>0.16500000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I87" s="6">
-        <v>0.752</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="J87" s="4">
-        <v>169.5</v>
+        <v>350.3</v>
       </c>
       <c r="K87" s="6">
-        <v>0.32900000000000001</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="L87" s="2">
-        <v>7.1999999999999886</v>
+        <v>-1.3000000000000109</v>
       </c>
       <c r="M87" s="6">
-        <v>0.12</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="N87" s="6">
-        <v>0.19</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="O87" s="8">
-        <v>5.774739583333333</v>
+        <v>20.202888583218709</v>
       </c>
       <c r="P87" s="9">
-        <v>14.709537572254341</v>
+        <v>19.30117994100295</v>
       </c>
       <c r="Q87" s="9">
-        <v>2.366865020127825</v>
+        <v>2.1617372195798019</v>
       </c>
       <c r="R87" s="10">
-        <v>48.117994100294993</v>
+        <v>36.01484441906937</v>
       </c>
       <c r="S87" s="6">
-        <v>0.12800760176557141</v>
+        <v>4.9967478385024203E-2</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B88" s="3">
         <v>46248</v>
       </c>
       <c r="C88" s="4">
-        <v>676</v>
+        <v>759</v>
       </c>
       <c r="D88" s="4">
-        <v>678</v>
+        <v>853</v>
       </c>
       <c r="E88" s="5">
-        <v>-2.9498525073746308E-3</v>
+        <v>-0.1101992966002345</v>
       </c>
       <c r="F88" s="4">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G88" s="6">
-        <v>0.16715976331360949</v>
+        <v>0.16205533596837951</v>
       </c>
       <c r="H88" s="7">
-        <v>0.16300000000000001</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="I88" s="6">
-        <v>0.81599999999999995</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="J88" s="4">
-        <v>229.76</v>
+        <v>317.83999999999997</v>
       </c>
       <c r="K88" s="6">
-        <v>0.33300000000000002</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="L88" s="2">
-        <v>-24.580000000000009</v>
+        <v>-41.94</v>
       </c>
       <c r="M88" s="6">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="N88" s="6">
-        <v>0.11600000000000001</v>
+        <v>0.182</v>
       </c>
       <c r="O88" s="8">
-        <v>6.2862426035502956</v>
+        <v>5.7517786561264828</v>
       </c>
       <c r="P88" s="9">
-        <v>14.371517996870111</v>
+        <v>14.35020746887967</v>
       </c>
       <c r="Q88" s="9">
-        <v>3.011073942816751</v>
+        <v>2.43620380166008</v>
       </c>
       <c r="R88" s="10">
-        <v>61.738335654596099</v>
+        <v>46.054618676063427</v>
       </c>
       <c r="S88" s="6">
-        <v>0.12478941798941801</v>
+        <v>0.1005267123287671</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B89" s="3">
         <v>46248</v>
       </c>
       <c r="C89" s="4">
-        <v>416</v>
+        <v>791</v>
       </c>
       <c r="D89" s="4">
-        <v>459</v>
+        <v>728</v>
       </c>
       <c r="E89" s="5">
-        <v>-9.3681917211328972E-2</v>
+        <v>8.6538461538461536E-2</v>
       </c>
       <c r="F89" s="4">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="G89" s="6">
-        <v>0.27163461538461542</v>
+        <v>0.18078381795195961</v>
       </c>
       <c r="H89" s="7">
-        <v>0.156</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="I89" s="6">
-        <v>0.78400000000000003</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="J89" s="4">
-        <v>222.84</v>
+        <v>330.59</v>
       </c>
       <c r="K89" s="6">
-        <v>0.35</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="L89" s="2">
-        <v>-4.6800000000000068</v>
+        <v>35.269999999999982</v>
       </c>
       <c r="M89" s="6">
-        <v>0.13900000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="N89" s="6">
-        <v>0.22</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="O89" s="8">
-        <v>6.867548076923077</v>
+        <v>6.8276864728192157</v>
       </c>
       <c r="P89" s="9">
-        <v>17.479015544041449</v>
+        <v>15.7844</v>
       </c>
       <c r="Q89" s="9">
-        <v>1.912861284929207</v>
+        <v>2.4556559750299618</v>
       </c>
       <c r="R89" s="10">
-        <v>34.356488960689283</v>
+        <v>43.32254454157718</v>
       </c>
       <c r="S89" s="6">
-        <v>8.1396692045156219E-2</v>
+        <v>6.8805291153415452E-2</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="B90" s="3">
         <v>46248</v>
       </c>
       <c r="C90" s="4">
-        <v>367</v>
+        <v>797</v>
       </c>
       <c r="D90" s="4">
-        <v>364</v>
+        <v>733</v>
       </c>
       <c r="E90" s="5">
-        <v>8.241758241758242E-3</v>
+        <v>8.7312414733969987E-2</v>
       </c>
       <c r="F90" s="4">
-        <v>75</v>
+        <v>207</v>
       </c>
       <c r="G90" s="6">
-        <v>0.20435967302452321</v>
+        <v>0.25972396486825589</v>
       </c>
       <c r="H90" s="7">
-        <v>0.13600000000000001</v>
+        <v>0.215</v>
       </c>
       <c r="I90" s="6">
-        <v>0.79500000000000004</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="J90" s="4">
-        <v>154.63</v>
+        <v>322.11</v>
       </c>
       <c r="K90" s="6">
         <v>0.30299999999999999</v>
       </c>
       <c r="L90" s="2">
-        <v>-15.31999999999999</v>
+        <v>17.949999999999989</v>
       </c>
       <c r="M90" s="6">
-        <v>0.14399999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="N90" s="6">
-        <v>0.17599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="O90" s="8">
-        <v>5.6544959128065386</v>
+        <v>11.909284818067761</v>
       </c>
       <c r="P90" s="9">
-        <v>14.86912181303116</v>
+        <v>15.495108695652171</v>
       </c>
       <c r="Q90" s="9">
-        <v>2.4042848507662709</v>
+        <v>2.577858850564732</v>
       </c>
       <c r="R90" s="10">
-        <v>50.4171247494018</v>
+        <v>45.89115519543013</v>
       </c>
       <c r="S90" s="6">
-        <v>0.14663673678809649</v>
+        <v>8.31710294317103E-2</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="B91" s="3">
         <v>46248</v>
       </c>
       <c r="C91" s="4">
-        <v>287</v>
+        <v>873</v>
       </c>
       <c r="D91" s="4">
-        <v>402</v>
+        <v>765</v>
       </c>
       <c r="E91" s="5">
-        <v>-0.28606965174129351</v>
+        <v>0.14117647058823529</v>
       </c>
       <c r="F91" s="4">
-        <v>71</v>
+        <v>162</v>
       </c>
       <c r="G91" s="6">
-        <v>0.2473867595818815</v>
+        <v>0.18556701030927841</v>
       </c>
       <c r="H91" s="7">
-        <v>0.11799999999999999</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="I91" s="6">
-        <v>0.71</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="J91" s="4">
-        <v>151.35</v>
+        <v>313.42</v>
       </c>
       <c r="K91" s="6">
-        <v>0.28799999999999998</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="L91" s="2">
-        <v>-47.31</v>
+        <v>36.610000000000007</v>
       </c>
       <c r="M91" s="6">
-        <v>0.28599999999999998</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="N91" s="6">
-        <v>0.35599999999999998</v>
+        <v>0.104</v>
       </c>
       <c r="O91" s="8">
-        <v>12.58432055749129</v>
+        <v>7.5775486827033216</v>
       </c>
       <c r="P91" s="9">
-        <v>16.6945652173913</v>
+        <v>15.26602641056423</v>
       </c>
       <c r="Q91" s="9">
-        <v>1.9318385453428371</v>
+        <v>2.8232961837954131</v>
       </c>
       <c r="R91" s="10">
-        <v>36.868186323092168</v>
+        <v>56.891710803394801</v>
       </c>
       <c r="S91" s="6">
-        <v>0.15555012667390519</v>
+        <v>0.17161036479118649</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="B92" s="3">
         <v>46248</v>
       </c>
       <c r="C92" s="4">
-        <v>334</v>
+        <v>936</v>
       </c>
       <c r="D92" s="4">
-        <v>378</v>
+        <v>831</v>
       </c>
       <c r="E92" s="5">
-        <v>-0.1164021164021164</v>
+        <v>0.1263537906137184</v>
       </c>
       <c r="F92" s="4">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="G92" s="6">
-        <v>0.29041916167664672</v>
+        <v>0.25961538461538458</v>
       </c>
       <c r="H92" s="7">
-        <v>8.5999999999999993E-2</v>
+        <v>0.248</v>
       </c>
       <c r="I92" s="6">
-        <v>0.60599999999999998</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="J92" s="4">
-        <v>169.07</v>
+        <v>336.22</v>
       </c>
       <c r="K92" s="6">
-        <v>0.31900000000000001</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="L92" s="2">
-        <v>-3.0600000000000018</v>
+        <v>40.470000000000027</v>
       </c>
       <c r="M92" s="6">
-        <v>0.19500000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="N92" s="6">
-        <v>0.26800000000000002</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="O92" s="8">
-        <v>7.5565868263473046</v>
+        <v>5.8522435897435896</v>
       </c>
       <c r="P92" s="9">
-        <v>16.31047297297297</v>
+        <v>15.124776785714291</v>
       </c>
       <c r="Q92" s="9">
-        <v>2.0023392187618518</v>
+        <v>2.8349842710218152</v>
       </c>
       <c r="R92" s="10">
-        <v>40.533506831489923</v>
+        <v>56.843733269882811</v>
       </c>
       <c r="S92" s="6">
-        <v>0.10060557420107979</v>
+        <v>0.1123464096789399</v>
       </c>
     </row>
   </sheetData>
